--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>91940</v>
+        <v>116840</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8366.66</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>83573.34</v>
+        <v>116840</v>
       </c>
     </row>
     <row r="3">
@@ -525,23 +525,23 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19389</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-19389</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="4">
@@ -567,31 +567,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>21420</v>
+        <v>26400</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11580</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9840</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>54820</v>
+        <v>64780</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6397.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>48422.5</v>
+        <v>64780</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>36440</v>
+        <v>41420</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34760</v>
+        <v>41420</v>
       </c>
     </row>
     <row r="7">
@@ -705,19 +705,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49800</v>
+        <v>59800</v>
       </c>
     </row>
     <row r="8">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47150</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>407.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-35570</v>
+        <v>11580</v>
       </c>
     </row>
     <row r="9">
@@ -789,19 +789,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="10">
@@ -831,19 +831,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47878</v>
+        <v>51858</v>
       </c>
     </row>
     <row r="11">
@@ -861,31 +861,31 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>31560</v>
+        <v>38160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>27580</v>
+        <v>38160</v>
       </c>
     </row>
     <row r="12">
@@ -903,31 +903,31 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>12490</v>
+        <v>32290</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5890</v>
+        <v>32290</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>129020</v>
+        <v>130418</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>161.3%</t>
+          <t>163.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>161.3%</t>
+          <t>163.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>129020</v>
+        <v>130418</v>
       </c>
     </row>
     <row r="14">
@@ -999,19 +999,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>60600</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="15">
@@ -1071,31 +1071,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>52738</v>
+        <v>47758</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>46138</v>
+        <v>47758</v>
       </c>
     </row>
     <row r="17">
@@ -1113,23 +1113,23 @@
         <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>27820</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-45600</v>
+        <v>27820</v>
       </c>
     </row>
     <row r="18">
@@ -1167,19 +1167,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-3020</v>
+        <v>13980</v>
       </c>
     </row>
     <row r="19">
@@ -1197,31 +1197,31 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>60920</v>
+        <v>67520</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>26920</v>
+        <v>67520</v>
       </c>
     </row>
     <row r="20">
@@ -1281,19 +1281,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>10000</v>
+        <v>26600</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10000</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="22">
@@ -1335,19 +1335,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="23">
@@ -1461,19 +1461,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13070</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8084</v>
+        <v>21154</v>
       </c>
     </row>
     <row r="26">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9786</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>60590</v>
+        <v>70376</v>
       </c>
     </row>
     <row r="27">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>18600</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-3660</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>29880</v>
+        <v>34860</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>25900</v>
+        <v>34860</v>
       </c>
     </row>
     <row r="30">
@@ -1671,19 +1671,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>35800</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="31">
@@ -1713,19 +1713,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17080</v>
+        <v>29800</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>131124</v>
+        <v>118404</v>
       </c>
     </row>
     <row r="32">
@@ -1743,31 +1743,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>68700</v>
+        <v>73680</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>64720</v>
+        <v>73680</v>
       </c>
     </row>
     <row r="33">
@@ -1785,31 +1785,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>27761</v>
+        <v>47422</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>17801</v>
+        <v>47422</v>
       </c>
     </row>
     <row r="34">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>33680</v>
+        <v>51110</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>33680</v>
+        <v>51110</v>
       </c>
     </row>
     <row r="36">
@@ -1911,31 +1911,31 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>45698</v>
+        <v>60638</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>41718</v>
+        <v>60638</v>
       </c>
     </row>
     <row r="37">
@@ -1953,31 +1953,31 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>29880</v>
+        <v>58116</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25900</v>
+        <v>58116</v>
       </c>
     </row>
     <row r="38">
@@ -1995,31 +1995,31 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>5700</v>
+        <v>44520</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>85708</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1503.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-80008</v>
+        <v>44520</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>71748</v>
+        <v>75548</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71748</v>
+        <v>75548</v>
       </c>
     </row>
     <row r="40">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>17240</v>
+        <v>18920</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -495,19 +495,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>8366.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>116840</v>
+        <v>108473.34</v>
       </c>
     </row>
     <row r="3">
@@ -537,19 +537,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>19389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>389.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4980</v>
+        <v>-14409</v>
       </c>
     </row>
     <row r="4">
@@ -579,19 +579,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>28380</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>26400</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="5">
@@ -621,19 +621,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6397.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>64780</v>
+        <v>58382.5</v>
       </c>
     </row>
     <row r="6">
@@ -663,19 +663,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41420</v>
+        <v>39740</v>
       </c>
     </row>
     <row r="7">
@@ -705,19 +705,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="8">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>47150</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>407.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11580</v>
+        <v>-35570</v>
       </c>
     </row>
     <row r="9">
@@ -789,19 +789,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4979</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>9961</v>
       </c>
     </row>
     <row r="10">
@@ -831,19 +831,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>51858</v>
+        <v>47878</v>
       </c>
     </row>
     <row r="11">
@@ -873,19 +873,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>38160</v>
+        <v>34180</v>
       </c>
     </row>
     <row r="12">
@@ -915,19 +915,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32290</v>
+        <v>25690</v>
       </c>
     </row>
     <row r="13">
@@ -999,19 +999,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>39800</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>75600</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="15">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47758</v>
+        <v>41158</v>
       </c>
     </row>
     <row r="17">
@@ -1125,19 +1125,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>52100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>187.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>27820</v>
+        <v>-24280</v>
       </c>
     </row>
     <row r="18">
@@ -1167,19 +1167,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13980</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="19">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>67520</v>
+        <v>33520</v>
       </c>
     </row>
     <row r="20">
@@ -1335,19 +1335,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -1461,19 +1461,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>13070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>21154</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="26">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>9786</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>70376</v>
+        <v>60590</v>
       </c>
     </row>
     <row r="27">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>14940</v>
+        <v>-3660</v>
       </c>
     </row>
     <row r="29">
@@ -1629,19 +1629,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>8960</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>34860</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="30">
@@ -1671,19 +1671,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47800</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="31">
@@ -1713,19 +1713,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29800</v>
+        <v>46880</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>118404</v>
+        <v>101324</v>
       </c>
     </row>
     <row r="32">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>73680</v>
+        <v>69700</v>
       </c>
     </row>
     <row r="33">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47422</v>
+        <v>37462</v>
       </c>
     </row>
     <row r="34">
@@ -1839,19 +1839,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>57619</v>
+        <v>54019</v>
       </c>
     </row>
     <row r="35">
@@ -1923,19 +1923,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>60638</v>
+        <v>56658</v>
       </c>
     </row>
     <row r="37">
@@ -1965,19 +1965,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>58116</v>
+        <v>54136</v>
       </c>
     </row>
     <row r="38">
@@ -2007,19 +2007,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>95508</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>214.5%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>44520</v>
+        <v>-50988</v>
       </c>
     </row>
     <row r="39">
@@ -2049,19 +2049,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3788</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>75548</v>
+        <v>71760</v>
       </c>
     </row>
     <row r="40">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>18920</v>
+        <v>17240</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>116840</v>
+        <v>119400</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8366.66</v>
+        <v>13346.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>108473.34</v>
+        <v>106053.34</v>
       </c>
     </row>
     <row r="3">
@@ -567,31 +567,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>26400</v>
+        <v>31778</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>28380</v>
+        <v>33360</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1980</v>
+        <v>-1582</v>
       </c>
     </row>
     <row r="5">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>59800</v>
+        <v>69760</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>58.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>49.8%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49800</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="8">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>14940</v>
+        <v>29880</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9961</v>
+        <v>24901</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>51858</v>
+        <v>77196</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47878</v>
+        <v>73216</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>38160</v>
+        <v>60518</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34180</v>
+        <v>56538</v>
       </c>
     </row>
     <row r="12">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>130418</v>
+        <v>135398</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>163.0%</t>
+          <t>169.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>163.0%</t>
+          <t>169.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>130418</v>
+        <v>135398</v>
       </c>
     </row>
     <row r="14">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>47758</v>
+        <v>49738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>41158</v>
+        <v>43138</v>
       </c>
     </row>
     <row r="17">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>41220</v>
+        <v>51220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>41220</v>
+        <v>51220</v>
       </c>
     </row>
     <row r="21">
@@ -1377,19 +1377,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>57580</v>
+        <v>50980</v>
       </c>
     </row>
     <row r="24">
@@ -1491,31 +1491,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>70376</v>
+        <v>107276</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9786</v>
+        <v>13766</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>60590</v>
+        <v>93510</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>24900</v>
+        <v>29880</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>24900</v>
+        <v>29880</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>14940</v>
+        <v>24900</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-3660</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>34860</v>
+        <v>49800</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>25900</v>
+        <v>40840</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>47800</v>
+        <v>62740</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>35800</v>
+        <v>50740</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>148204</v>
+        <v>150694</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>101324</v>
+        <v>103814</v>
       </c>
     </row>
     <row r="32">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>47422</v>
+        <v>52402</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37462</v>
+        <v>42442</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>57619</v>
+        <v>62599</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54019</v>
+        <v>58999</v>
       </c>
     </row>
     <row r="35">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>60638</v>
+        <v>62318</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>56658</v>
+        <v>58338</v>
       </c>
     </row>
     <row r="37">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>44520</v>
+        <v>83340</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>214.5%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-50988</v>
+        <v>-12168</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>75548</v>
+        <v>80528</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71760</v>
+        <v>76740</v>
       </c>
     </row>
     <row r="40">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>18920</v>
+        <v>28880</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>17240</v>
+        <v>27200</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -495,19 +495,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13346.66</v>
+        <v>18326.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>106053.34</v>
+        <v>101073.34</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>4980</v>
+        <v>6960</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>389.3%</t>
+          <t>278.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-14409</v>
+        <v>-12429</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>31778</v>
+        <v>41678</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1582</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="5">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>69760</v>
+        <v>74740</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59760</v>
+        <v>64740</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>11580</v>
+        <v>21540</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>407.2%</t>
+          <t>218.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-35570</v>
+        <v>-25610</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>29880</v>
+        <v>36480</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24901</v>
+        <v>31501</v>
       </c>
     </row>
     <row r="10">
@@ -831,19 +831,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3980</v>
+        <v>7959</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>73216</v>
+        <v>69237</v>
       </c>
     </row>
     <row r="11">
@@ -945,31 +945,31 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>135398</v>
+        <v>141338</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>169.2%</t>
+          <t>176.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>169.2%</t>
+          <t>165.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>135398</v>
+        <v>132338</v>
       </c>
     </row>
     <row r="14">
@@ -999,19 +999,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39800</v>
+        <v>69600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>35800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>49738</v>
+        <v>59738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>43138</v>
+        <v>53138</v>
       </c>
     </row>
     <row r="17">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>51220</v>
+        <v>59220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51220</v>
+        <v>59220</v>
       </c>
     </row>
     <row r="21">
@@ -1323,19 +1323,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>6600</v>
+        <v>26400</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>57580</v>
+        <v>59560</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>50980</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="24">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>21154</v>
+        <v>26134</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8084</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>107276</v>
+        <v>137236</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>93510</v>
+        <v>123470</v>
       </c>
     </row>
     <row r="27">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>24900</v>
+        <v>39840</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6300</v>
+        <v>21240</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>49800</v>
+        <v>54780</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>40840</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="30">
@@ -1659,14 +1659,14 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>62740</v>
+        <v>67720</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1675,11 +1675,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>150694</v>
+        <v>163474</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>103814</v>
+        <v>116594</v>
       </c>
     </row>
     <row r="32">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>52402</v>
+        <v>57382</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>42442</v>
+        <v>47422</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>62599</v>
+        <v>57819</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>58999</v>
+        <v>54219</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>51110</v>
+        <v>57710</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>51110</v>
+        <v>57710</v>
       </c>
     </row>
     <row r="36">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>58116</v>
+        <v>63096</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>54136</v>
+        <v>59116</v>
       </c>
     </row>
     <row r="38">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>28880</v>
+        <v>33860</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>27200</v>
+        <v>32180</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -495,19 +495,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18326.66</v>
+        <v>38126.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>101073.34</v>
+        <v>81273.34</v>
       </c>
     </row>
     <row r="3">
@@ -567,31 +567,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>41678</v>
+        <v>43658</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>33360</v>
+        <v>44560</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8318</v>
+        <v>-902</v>
       </c>
     </row>
     <row r="5">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>41420</v>
+        <v>43400</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>39740</v>
+        <v>41720</v>
       </c>
     </row>
     <row r="7">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>32290</v>
+        <v>59110</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>25690</v>
+        <v>52510</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>75600</v>
+        <v>114420</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6000</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>398</v>
+        <v>-2802</v>
       </c>
     </row>
     <row r="16">
@@ -1071,31 +1071,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>59738</v>
+        <v>60136</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6600</v>
+        <v>36400</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>53138</v>
+        <v>23736</v>
       </c>
     </row>
     <row r="17">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>13980</v>
+        <v>14980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-3020</v>
+        <v>-2020</v>
       </c>
     </row>
     <row r="19">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>59220</v>
+        <v>69220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>59220</v>
+        <v>69220</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>26600</v>
+        <v>38600</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26600</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="22">
@@ -1449,14 +1449,14 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>26134</v>
+        <v>31114</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13070</v>
+        <v>18050</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>137236</v>
+        <v>142216</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>123470</v>
+        <v>128450</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>29880</v>
+        <v>33580</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>29880</v>
+        <v>33580</v>
       </c>
     </row>
     <row r="28">
@@ -1617,31 +1617,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>54780</v>
+        <v>61380</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8960</v>
+        <v>12940</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>45820</v>
+        <v>48440</v>
       </c>
     </row>
     <row r="30">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9960</v>
+        <v>24780</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47422</v>
+        <v>32602</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>57819</v>
+        <v>58019</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54219</v>
+        <v>54419</v>
       </c>
     </row>
     <row r="35">
@@ -1965,19 +1965,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>59116</v>
+        <v>55136</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>83340</v>
+        <v>125860</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-12168</v>
+        <v>30352</v>
       </c>
     </row>
     <row r="39">
@@ -2037,31 +2037,31 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>80528</v>
+        <v>86228</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3788</v>
+        <v>16896</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>76740</v>
+        <v>69332</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>119400</v>
+        <v>156416</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>81273.34</v>
+        <v>118289.34</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>6960</v>
+        <v>62520</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>278.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-12429</v>
+        <v>43131</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>43658</v>
+        <v>48638</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-902</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>64780</v>
+        <v>74740</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>58382.5</v>
+        <v>68342.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>43400</v>
+        <v>48380</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41720</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="7">
@@ -735,19 +735,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>21540</v>
+        <v>54340</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>218.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-25610</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>36480</v>
+        <v>43080</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31501</v>
+        <v>38101</v>
       </c>
     </row>
     <row r="10">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>59110</v>
+        <v>64090</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>52510</v>
+        <v>57490</v>
       </c>
     </row>
     <row r="13">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>60136</v>
+        <v>60734</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23736</v>
+        <v>24334</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>26400</v>
+        <v>51200</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>18800</v>
+        <v>43600</v>
       </c>
     </row>
     <row r="23">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13766</v>
+        <v>18746</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>128450</v>
+        <v>123470</v>
       </c>
     </row>
     <row r="27">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>67720</v>
+        <v>72700</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>50740</v>
+        <v>55720</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>163474</v>
+        <v>173434</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>116594</v>
+        <v>126554</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>73680</v>
+        <v>78660</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>69700</v>
+        <v>74680</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>57382</v>
+        <v>62362</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>32602</v>
+        <v>37582</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>58019</v>
+        <v>67979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54419</v>
+        <v>64379</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>57710</v>
+        <v>72650</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>57710</v>
+        <v>72650</v>
       </c>
     </row>
     <row r="36">
@@ -1911,31 +1911,31 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>62318</v>
+        <v>82238</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>58338</v>
+        <v>74278</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>63096</v>
+        <v>83016</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>55136</v>
+        <v>75056</v>
       </c>
     </row>
     <row r="38">
@@ -2091,19 +2091,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>8780</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>33860</v>
+        <v>48800</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>32180</v>
+        <v>47120</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>156416</v>
+        <v>169152</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>118289.34</v>
+        <v>131025.34</v>
       </c>
     </row>
     <row r="3">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48638</v>
+        <v>45698</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4078</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>74740</v>
+        <v>84700</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>68342.5</v>
+        <v>78302.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>48380</v>
+        <v>52340</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>46700</v>
+        <v>50660</v>
       </c>
     </row>
     <row r="7">
@@ -705,19 +705,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>14980</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>64740</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>54340</v>
+        <v>56320</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7190</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="9">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>64090</v>
+        <v>78910</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>57490</v>
+        <v>72310</v>
       </c>
     </row>
     <row r="13">
@@ -945,31 +945,31 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>141338</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>176.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>165.4%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9000</v>
+        <v>33800</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>132338</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>60734</v>
+        <v>70634</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24334</v>
+        <v>34234</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>27820</v>
+        <v>28020</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>187.3%</t>
+          <t>185.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-24280</v>
+        <v>-24080</v>
       </c>
     </row>
     <row r="18">
@@ -1155,31 +1155,31 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>14980</v>
+        <v>21580</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17000</v>
+        <v>20200</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-2020</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67520</v>
+        <v>67720</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33520</v>
+        <v>33720</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>69220</v>
+        <v>87820</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>69220</v>
+        <v>87820</v>
       </c>
     </row>
     <row r="21">
@@ -1407,31 +1407,31 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>30600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="25">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>142216</v>
+        <v>138236</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>123470</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="27">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>173434</v>
+        <v>183394</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>126554</v>
+        <v>136514</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>78660</v>
+        <v>105180</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>74680</v>
+        <v>101200</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>62362</v>
+        <v>67342</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37582</v>
+        <v>42562</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>67979</v>
+        <v>77979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>64379</v>
+        <v>74379</v>
       </c>
     </row>
     <row r="35">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>83016</v>
+        <v>87996</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>75056</v>
+        <v>80036</v>
       </c>
     </row>
     <row r="38">
@@ -2121,31 +2121,31 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>48800</v>
+        <v>58760</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1680</v>
+        <v>4997</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>47120</v>
+        <v>53763</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -570,11 +570,11 @@
         <v>45698</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1452,11 +1452,11 @@
         <v>31114</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1662,11 +1662,11 @@
         <v>72700</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1872,11 +1872,11 @@
         <v>72650</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2040,11 +2040,11 @@
         <v>86228</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>169152</v>
+        <v>170432</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>131025.34</v>
+        <v>132305.34</v>
       </c>
     </row>
     <row r="3">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>45698</v>
+        <v>40718</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1138</v>
+        <v>-3842</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>84700</v>
+        <v>89680</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>78302.5</v>
+        <v>83282.5</v>
       </c>
     </row>
     <row r="6">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47150</v>
+        <v>51333</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9170</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="9">
@@ -789,19 +789,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4979</v>
+        <v>11579</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>38101</v>
+        <v>31501</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>77196</v>
+        <v>72216</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>69237</v>
+        <v>64257</v>
       </c>
     </row>
     <row r="11">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>78910</v>
+        <v>118510</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>134.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>72310</v>
+        <v>111910</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>154178</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>192.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>150.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>120378</v>
       </c>
     </row>
     <row r="14">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67720</v>
+        <v>39920</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33720</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="20">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>31114</v>
+        <v>30716</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13064</v>
+        <v>12666</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>138236</v>
+        <v>131596</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>119490</v>
+        <v>112850</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>33580</v>
+        <v>28600</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>33580</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>39840</v>
+        <v>36840</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>21240</v>
+        <v>18240</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>61380</v>
+        <v>56400</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>12940</v>
+        <v>17123</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>48440</v>
+        <v>39277</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>72700</v>
+        <v>64740</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>55720</v>
+        <v>47760</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>183394</v>
+        <v>189994</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>136514</v>
+        <v>143114</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>105180</v>
+        <v>93578</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>101200</v>
+        <v>89598</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>67342</v>
+        <v>77740</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>42562</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>77979</v>
+        <v>73999</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>74379</v>
+        <v>70399</v>
       </c>
     </row>
     <row r="35">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>82238</v>
+        <v>87218</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>74278</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="37">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>86228</v>
+        <v>84168</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>69332</v>
+        <v>67272</v>
       </c>
     </row>
     <row r="40">
@@ -2079,19 +2079,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>8780</v>
+        <v>4980</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2099,11 +2099,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>160.6%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>780</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="41">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>58760</v>
+        <v>59760</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>53763</v>
+        <v>54763</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>40718</v>
+        <v>45698</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-3842</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>72216</v>
+        <v>77196</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>64257</v>
+        <v>69237</v>
       </c>
     </row>
     <row r="11">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>154178</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>192.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>150.5%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>120378</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>39920</v>
+        <v>67720</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5920</v>
+        <v>33720</v>
       </c>
     </row>
     <row r="20">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>30716</v>
+        <v>31114</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12666</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>131596</v>
+        <v>145576</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>112850</v>
+        <v>126830</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>28600</v>
+        <v>33580</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>28600</v>
+        <v>33580</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>36840</v>
+        <v>41820</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>18240</v>
+        <v>23220</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>56400</v>
+        <v>61380</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>39277</v>
+        <v>44257</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>64740</v>
+        <v>72700</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47760</v>
+        <v>55720</v>
       </c>
     </row>
     <row r="31">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>93578</v>
+        <v>105578</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>89598</v>
+        <v>101598</v>
       </c>
     </row>
     <row r="33">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>73999</v>
+        <v>77979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>70399</v>
+        <v>74379</v>
       </c>
     </row>
     <row r="35">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>84168</v>
+        <v>88128</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>67272</v>
+        <v>71232</v>
       </c>
     </row>
     <row r="40">
@@ -2079,19 +2079,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>4980</v>
+        <v>8780</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2099,11 +2099,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>160.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-3020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>59760</v>
+        <v>63740</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>54763</v>
+        <v>58743</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>158138</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>197.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>155.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>124338</v>
       </c>
     </row>
     <row r="14">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>59560</v>
+        <v>31760</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>52960</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="24">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>158138</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>197.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>155.4%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>124338</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>31760</v>
+        <v>59560</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25160</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="24">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>170432</v>
+        <v>225012</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>132305.34</v>
+        <v>186885.34</v>
       </c>
     </row>
     <row r="3">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>89680</v>
+        <v>94660</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>83282.5</v>
+        <v>88262.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>52340</v>
+        <v>57320</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50660</v>
+        <v>55640</v>
       </c>
     </row>
     <row r="7">
@@ -693,31 +693,31 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>74740</v>
+        <v>109600</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14980</v>
+        <v>19130</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59760</v>
+        <v>90470</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>56320</v>
+        <v>81220</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4987</v>
+        <v>29887</v>
       </c>
     </row>
     <row r="9">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>207738</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>259.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>217.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>173938</v>
       </c>
     </row>
     <row r="14">
@@ -999,19 +999,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>69600</v>
+        <v>78600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>44820</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>70634</v>
+        <v>77234</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>34234</v>
+        <v>40834</v>
       </c>
     </row>
     <row r="17">
@@ -1365,19 +1365,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>59560</v>
+        <v>31760</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>52960</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>30600</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>30600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>31114</v>
+        <v>41074</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13064</v>
+        <v>23024</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>145576</v>
+        <v>176956</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>126830</v>
+        <v>158210</v>
       </c>
     </row>
     <row r="27">
@@ -1533,31 +1533,31 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>33580</v>
+        <v>43540</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>33580</v>
+        <v>39840</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>41820</v>
+        <v>56760</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>23220</v>
+        <v>38160</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>61380</v>
+        <v>71738</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>44257</v>
+        <v>54615</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>72700</v>
+        <v>87640</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>55720</v>
+        <v>70660</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>189994</v>
+        <v>208594</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>130.4%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>46880</v>
+        <v>51860</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>143114</v>
+        <v>156734</v>
       </c>
     </row>
     <row r="32">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>101598</v>
+        <v>97618</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>77740</v>
+        <v>82740</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>52960</v>
+        <v>57960</v>
       </c>
     </row>
     <row r="34">
@@ -1827,31 +1827,31 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>77979</v>
+        <v>87939</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3600</v>
+        <v>7500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>74379</v>
+        <v>80439</v>
       </c>
     </row>
     <row r="35">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>87218</v>
+        <v>105958</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>79258</v>
+        <v>97998</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>87996</v>
+        <v>92976</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>80036</v>
+        <v>85016</v>
       </c>
     </row>
     <row r="38">
@@ -2037,31 +2037,31 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>88128</v>
+        <v>91928</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>16896</v>
+        <v>54073</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71232</v>
+        <v>37855</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>225012</v>
+        <v>224312</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>38126.66</v>
+        <v>41598.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>186885.34</v>
+        <v>182713.34</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>62520</v>
+        <v>64200</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43131</v>
+        <v>44811</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>45698</v>
+        <v>52036</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1138</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>94660</v>
+        <v>96640</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>88262.5</v>
+        <v>90242.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>57320</v>
+        <v>53360</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1680</v>
+        <v>11680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>55640</v>
+        <v>41680</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>109600</v>
+        <v>104620</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>90470</v>
+        <v>85490</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>81220</v>
+        <v>86200</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29887</v>
+        <v>34867</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>77196</v>
+        <v>83796</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>69237</v>
+        <v>75837</v>
       </c>
     </row>
     <row r="11">
@@ -873,19 +873,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3980</v>
+        <v>8960</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>56538</v>
+        <v>51558</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>118510</v>
+        <v>91690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>134.7%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>111910</v>
+        <v>85090</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>114420</v>
+        <v>75600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>35820</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="15">
@@ -1071,31 +1071,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>77234</v>
+        <v>122834</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>36400</v>
+        <v>43000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>40834</v>
+        <v>79834</v>
       </c>
     </row>
     <row r="17">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>21580</v>
+        <v>20580</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1380</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>38600</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="22">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>41074</v>
+        <v>51034</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>23024</v>
+        <v>32984</v>
       </c>
     </row>
     <row r="26">
@@ -1533,14 +1533,14 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>43540</v>
+        <v>48520</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3700</v>
+        <v>8680</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>71738</v>
+        <v>83318</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>54615</v>
+        <v>66195</v>
       </c>
     </row>
     <row r="30">
@@ -1659,14 +1659,14 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>87640</v>
+        <v>92620</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1675,11 +1675,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16980</v>
+        <v>21960</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>208594</v>
+        <v>213574</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>130.4%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>156734</v>
+        <v>161714</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>105578</v>
+        <v>140358</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>97618</v>
+        <v>132398</v>
       </c>
     </row>
     <row r="33">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4997</v>
+        <v>9977</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>58743</v>
+        <v>53763</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>224312</v>
+        <v>230912</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>182713.34</v>
+        <v>189313.34</v>
       </c>
     </row>
     <row r="3">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>53360</v>
+        <v>78160</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41680</v>
+        <v>66480</v>
       </c>
     </row>
     <row r="7">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51333</v>
+        <v>53125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>34867</v>
+        <v>33075</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>83796</v>
+        <v>91956</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>75837</v>
+        <v>83997</v>
       </c>
     </row>
     <row r="11">
@@ -873,19 +873,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8960</v>
+        <v>13940</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51558</v>
+        <v>46578</v>
       </c>
     </row>
     <row r="12">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>207738</v>
+        <v>182938</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>259.7%</t>
+          <t>228.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>217.4%</t>
+          <t>186.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>173938</v>
+        <v>149138</v>
       </c>
     </row>
     <row r="14">
@@ -987,31 +987,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>75600</v>
+        <v>83700</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>78600</v>
+        <v>124200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>148.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-3000</v>
+        <v>-40500</v>
       </c>
     </row>
     <row r="15">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>20580</v>
+        <v>98196</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>380</v>
+        <v>77996</v>
       </c>
     </row>
     <row r="19">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34000</v>
+        <v>50800</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33720</v>
+        <v>16920</v>
       </c>
     </row>
     <row r="20">
@@ -1281,19 +1281,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>38600</v>
+        <v>45200</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>25400</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="22">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>176956</v>
+        <v>181936</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>158210</v>
+        <v>163190</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>48520</v>
+        <v>53500</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>39840</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="28">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>92620</v>
+        <v>104560</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>70660</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>213574</v>
+        <v>218554</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>102.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>51860</v>
+        <v>54340</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>161714</v>
+        <v>164214</v>
       </c>
     </row>
     <row r="32">
@@ -1743,31 +1743,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>140358</v>
+        <v>196958</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7960</v>
+        <v>20940</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>132398</v>
+        <v>176018</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>82740</v>
+        <v>83138</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>57960</v>
+        <v>58358</v>
       </c>
     </row>
     <row r="34">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>92976</v>
+        <v>100936</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>97.1%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>89.4%</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>81.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>85016</v>
+        <v>92976</v>
       </c>
     </row>
     <row r="38">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>91928</v>
+        <v>96908</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>37855</v>
+        <v>42835</v>
       </c>
     </row>
     <row r="40">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>230912</v>
+        <v>250832</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>189313.34</v>
+        <v>209233.34</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>64200</v>
+        <v>69180</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>44811</v>
+        <v>49791</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>52036</v>
+        <v>57016</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7476</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>96640</v>
+        <v>111580</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>90242.5</v>
+        <v>105182.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>78160</v>
+        <v>93100</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>66480</v>
+        <v>81420</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>104620</v>
+        <v>106300</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>85490</v>
+        <v>87170</v>
       </c>
     </row>
     <row r="8">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>53125</v>
+        <v>56825</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>33075</v>
+        <v>29375</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>91956</v>
+        <v>92752</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>83997</v>
+        <v>84793</v>
       </c>
     </row>
     <row r="11">
@@ -957,19 +957,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>186.4%</t>
+          <t>214.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>33800</v>
+        <v>10980</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>149138</v>
+        <v>171958</v>
       </c>
     </row>
     <row r="14">
@@ -987,31 +987,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>83700</v>
+        <v>84200</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>124200</v>
+        <v>132380</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>148.4%</t>
+          <t>157.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-40500</v>
+        <v>-48180</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>122834</v>
+        <v>123572</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>128.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>79834</v>
+        <v>80572</v>
       </c>
     </row>
     <row r="17">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>98196</v>
+        <v>107398</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>77996</v>
+        <v>87198</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67720</v>
+        <v>74320</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16920</v>
+        <v>23520</v>
       </c>
     </row>
     <row r="20">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>13200</v>
+        <v>38000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>32000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="22">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>181936</v>
+        <v>186916</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>163190</v>
+        <v>168170</v>
       </c>
     </row>
     <row r="27">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>56760</v>
+        <v>57158</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>38160</v>
+        <v>38558</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>83318</v>
+        <v>88298</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>66195</v>
+        <v>71175</v>
       </c>
     </row>
     <row r="30">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>218554</v>
+        <v>238514</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>149.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>102.6%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>164214</v>
+        <v>184174</v>
       </c>
     </row>
     <row r="32">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>83138</v>
+        <v>89618</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>58358</v>
+        <v>64838</v>
       </c>
     </row>
     <row r="34">
@@ -1827,31 +1827,31 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>87939</v>
+        <v>97899</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>80439</v>
+        <v>88399</v>
       </c>
     </row>
     <row r="35">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>105958</v>
+        <v>126874</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>97998</v>
+        <v>118914</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>100936</v>
+        <v>130816</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>92976</v>
+        <v>122856</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>125860</v>
+        <v>137860</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>30352</v>
+        <v>42352</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>96908</v>
+        <v>91928</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>42835</v>
+        <v>37855</v>
       </c>
     </row>
     <row r="40">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>63740</v>
+        <v>84058</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>53763</v>
+        <v>74081</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>111580</v>
+        <v>111978</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>105182.5</v>
+        <v>105580.5</v>
       </c>
     </row>
     <row r="6">
@@ -1239,19 +1239,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>87820</v>
+        <v>94420</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87820</v>
+        <v>94420</v>
       </c>
     </row>
     <row r="21">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>51034</v>
+        <v>56014</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>32984</v>
+        <v>37964</v>
       </c>
     </row>
     <row r="26">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>57158</v>
+        <v>58838</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>38558</v>
+        <v>40238</v>
       </c>
     </row>
     <row r="29">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>238514</v>
+        <v>243494</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>149.1%</t>
+          <t>152.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>118.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>184174</v>
+        <v>189154</v>
       </c>
     </row>
     <row r="32">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>72650</v>
+        <v>79250</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>72650</v>
+        <v>79250</v>
       </c>
     </row>
     <row r="36">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>137860</v>
+        <v>139840</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>42352</v>
+        <v>44332</v>
       </c>
     </row>
     <row r="39">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>69180</v>
+        <v>69479</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49791</v>
+        <v>50090</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>57016</v>
+        <v>61996</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12456</v>
+        <v>17436</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>111978</v>
+        <v>116958</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6397.5</v>
+        <v>7887.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>105580.5</v>
+        <v>109070.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>93100</v>
+        <v>95080</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11680</v>
+        <v>15660</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>81420</v>
+        <v>79420</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>106300</v>
+        <v>116260</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>87170</v>
+        <v>97130</v>
       </c>
     </row>
     <row r="8">
@@ -747,19 +747,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>56825</v>
+        <v>82422</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29375</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>92752</v>
+        <v>119352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>84793</v>
+        <v>111393</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>60518</v>
+        <v>85418</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46578</v>
+        <v>71478</v>
       </c>
     </row>
     <row r="12">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>182938</v>
+        <v>242538</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>228.7%</t>
+          <t>303.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>214.9%</t>
+          <t>289.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>171958</v>
+        <v>231558</v>
       </c>
     </row>
     <row r="14">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43000</v>
+        <v>67800</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>80572</v>
+        <v>55772</v>
       </c>
     </row>
     <row r="17">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>107398</v>
+        <v>113998</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>87198</v>
+        <v>93798</v>
       </c>
     </row>
     <row r="19">
@@ -1251,19 +1251,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>94420</v>
+        <v>87820</v>
       </c>
     </row>
     <row r="21">
@@ -1407,31 +1407,31 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>56014</v>
+        <v>60994</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>37964</v>
+        <v>42944</v>
       </c>
     </row>
     <row r="26">
@@ -1491,31 +1491,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>186916</v>
+        <v>221696</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>138.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>119.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18746</v>
+        <v>30326</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>168170</v>
+        <v>191370</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>53500</v>
+        <v>63460</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44820</v>
+        <v>54780</v>
       </c>
     </row>
     <row r="28">
@@ -1575,31 +1575,31 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>58838</v>
+        <v>68798</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>18600</v>
+        <v>25200</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>40238</v>
+        <v>43598</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>88298</v>
+        <v>103238</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>17123</v>
+        <v>22103</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>71175</v>
+        <v>81135</v>
       </c>
     </row>
     <row r="30">
@@ -1659,31 +1659,31 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>104560</v>
+        <v>114520</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>21960</v>
+        <v>24613.4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>82600</v>
+        <v>89906.60000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>243494</v>
+        <v>250094</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>152.2%</t>
+          <t>156.3%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>189154</v>
+        <v>195754</v>
       </c>
     </row>
     <row r="32">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20940</v>
+        <v>25940</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>176018</v>
+        <v>171018</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>89618</v>
+        <v>91118</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>64838</v>
+        <v>66338</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>97899</v>
+        <v>103217</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>88399</v>
+        <v>93717</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>79250</v>
+        <v>84230</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>79250</v>
+        <v>84230</v>
       </c>
     </row>
     <row r="36">
@@ -1953,31 +1953,31 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>130816</v>
+        <v>150816</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>145.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7960</v>
+        <v>12940</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>122856</v>
+        <v>137876</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>139840</v>
+        <v>141820</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>44332</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="39">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -495,19 +495,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41598.66</v>
+        <v>44598.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>209233.34</v>
+        <v>206233.34</v>
       </c>
     </row>
     <row r="3">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -525,19 +525,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>69479</v>
+        <v>76079</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>50090</v>
+        <v>56690</v>
       </c>
     </row>
     <row r="4">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>116958</v>
+        <v>136958</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>109070.5</v>
+        <v>129070.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>95080</v>
+        <v>101740</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>79420</v>
+        <v>86080</v>
       </c>
     </row>
     <row r="7">
@@ -735,31 +735,31 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>86200</v>
+        <v>21540</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>82422</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3778</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="9">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>91690</v>
+        <v>101690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>85090</v>
+        <v>95090</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>242538</v>
+        <v>212738</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>303.2%</t>
+          <t>265.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>289.4%</t>
+          <t>252.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>231558</v>
+        <v>201758</v>
       </c>
     </row>
     <row r="14">
@@ -1071,19 +1071,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>123572</v>
+        <v>130172</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>128.7%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>55772</v>
+        <v>62372</v>
       </c>
     </row>
     <row r="17">
@@ -1155,19 +1155,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>113998</v>
+        <v>117298</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>133.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>93798</v>
+        <v>97098</v>
       </c>
     </row>
     <row r="19">
@@ -1281,19 +1281,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>45200</v>
+        <v>55200</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7200</v>
+        <v>17200</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>51200</v>
+        <v>78020</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>43600</v>
+        <v>70420</v>
       </c>
     </row>
     <row r="23">
@@ -1449,19 +1449,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>60994</v>
+        <v>65974</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>42944</v>
+        <v>47924</v>
       </c>
     </row>
     <row r="26">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>119.6%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30326</v>
+        <v>35306</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>191370</v>
+        <v>186390</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>63460</v>
+        <v>58480</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>54780</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>68798</v>
+        <v>93598</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>43598</v>
+        <v>68398</v>
       </c>
     </row>
     <row r="29">
@@ -1629,19 +1629,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22103</v>
+        <v>27083</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>81135</v>
+        <v>76155</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>114520</v>
+        <v>119500</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>89906.60000000001</v>
+        <v>94886.60000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>91118</v>
+        <v>106118</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>66338</v>
+        <v>81338</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>103217</v>
+        <v>113217</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>93717</v>
+        <v>103717</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>84230</v>
+        <v>89210</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>84230</v>
+        <v>89210</v>
       </c>
     </row>
     <row r="36">
@@ -1995,19 +1995,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>141820</v>
+        <v>143720</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>46312</v>
+        <v>48212</v>
       </c>
     </row>
     <row r="39">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9977</v>
+        <v>14957</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>74081</v>
+        <v>69101</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -567,19 +567,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>61996</v>
+        <v>86796</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17436</v>
+        <v>42236</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>136958</v>
+        <v>166738</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>138.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>129070.5</v>
+        <v>158850.5</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>101740</v>
+        <v>106720</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>86080</v>
+        <v>91060</v>
       </c>
     </row>
     <row r="7">
@@ -777,19 +777,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>43080</v>
+        <v>48060</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31501</v>
+        <v>36481</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>119352</v>
+        <v>129352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>111393</v>
+        <v>121393</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>85418</v>
+        <v>90418</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71478</v>
+        <v>76478</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>101690</v>
+        <v>111690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>95090</v>
+        <v>105090</v>
       </c>
     </row>
     <row r="13">
@@ -945,19 +945,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>212738</v>
+        <v>357538</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>265.9%</t>
+          <t>446.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>252.2%</t>
+          <t>433.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -965,11 +965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>201758</v>
+        <v>346558</v>
       </c>
     </row>
     <row r="14">
@@ -1029,19 +1029,19 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>10398</v>
+        <v>11398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1049,11 +1049,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-2802</v>
+        <v>-1802</v>
       </c>
     </row>
     <row r="16">
@@ -1167,19 +1167,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20200</v>
+        <v>38416</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>97098</v>
+        <v>78882</v>
       </c>
     </row>
     <row r="19">
@@ -1251,19 +1251,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87820</v>
+        <v>81220</v>
       </c>
     </row>
     <row r="21">
@@ -1323,19 +1323,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>78020</v>
+        <v>123620</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>154.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>145.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>70420</v>
+        <v>116020</v>
       </c>
     </row>
     <row r="23">
@@ -1491,19 +1491,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>221696</v>
+        <v>253096</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>138.6%</t>
+          <t>158.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1511,11 +1511,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>186390</v>
+        <v>217790</v>
       </c>
     </row>
     <row r="27">
@@ -1545,19 +1545,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8680</v>
+        <v>13660</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>49800</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>93598</v>
+        <v>108418</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>68398</v>
+        <v>83218</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>103238</v>
+        <v>114818</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>76155</v>
+        <v>87735</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>119500</v>
+        <v>127040</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>94886.60000000001</v>
+        <v>102426.6</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>250094</v>
+        <v>265034</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>156.3%</t>
+          <t>165.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>54340</v>
+        <v>84120</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>195754</v>
+        <v>180914</v>
       </c>
     </row>
     <row r="32">
@@ -1785,19 +1785,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>106118</v>
+        <v>111098</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>81338</v>
+        <v>86318</v>
       </c>
     </row>
     <row r="34">
@@ -1827,19 +1827,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>113217</v>
+        <v>127858</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>103717</v>
+        <v>118358</v>
       </c>
     </row>
     <row r="35">
@@ -1869,19 +1869,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>89210</v>
+        <v>104150</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>89210</v>
+        <v>104150</v>
       </c>
     </row>
     <row r="36">
@@ -1911,19 +1911,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>126874</v>
+        <v>131854</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>137.3%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>118914</v>
+        <v>123894</v>
       </c>
     </row>
     <row r="37">
@@ -1953,19 +1953,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>150816</v>
+        <v>155796</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>145.0%</t>
+          <t>149.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>137.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>137876</v>
+        <v>142856</v>
       </c>
     </row>
     <row r="38">
@@ -2121,19 +2121,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>84058</v>
+        <v>89038</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>69101</v>
+        <v>74081</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,283 +471,283 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>240000</v>
+        <v>191500</v>
       </c>
       <c r="D2" t="n">
-        <v>250832</v>
+        <v>6774</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44598.66</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>206233.34</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>160000</v>
+        <v>185200</v>
       </c>
       <c r="D3" t="n">
-        <v>76079</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19389</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>56690</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120000</v>
+        <v>165200</v>
       </c>
       <c r="D4" t="n">
-        <v>86796</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10398</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>44560</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>42236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>高铭瑞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120000</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="n">
-        <v>166738</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7887.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>158850.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120000</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="n">
-        <v>106720</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15660</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>91060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120000</v>
+        <v>148350</v>
       </c>
       <c r="D7" t="n">
-        <v>116260</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19130</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>97130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>160000</v>
+        <v>115750</v>
       </c>
       <c r="D8" t="n">
-        <v>21540</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -759,667 +759,667 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21540</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80000</v>
+        <v>207250</v>
       </c>
       <c r="D9" t="n">
-        <v>48060</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11579</v>
+        <v>45600</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36481</v>
+        <v>-45600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160000</v>
+        <v>168625</v>
       </c>
       <c r="D10" t="n">
-        <v>129352</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7959</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>121393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120000</v>
+        <v>168625</v>
       </c>
       <c r="D11" t="n">
-        <v>90418</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>13940</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>76478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>88000</v>
+        <v>148625</v>
       </c>
       <c r="D12" t="n">
-        <v>111690</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>105090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80000</v>
+        <v>141500</v>
       </c>
       <c r="D13" t="n">
-        <v>357538</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>446.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>433.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>346558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96000</v>
+        <v>128625</v>
       </c>
       <c r="D14" t="n">
-        <v>84200</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>132380</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>157.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-48180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80000</v>
+        <v>91500</v>
       </c>
       <c r="D15" t="n">
-        <v>11398</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>96000</v>
+        <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>130172</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>67800</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>62372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80000</v>
+        <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>28020</v>
+        <v>30458</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>185.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-24080</v>
+        <v>30458</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>88000</v>
+        <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>117298</v>
+        <v>4980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>38416</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>78882</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88000</v>
+        <v>178900</v>
       </c>
       <c r="D19" t="n">
-        <v>74320</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>50800</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>88000</v>
+        <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>94420</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>81220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>88000</v>
+        <v>95750</v>
       </c>
       <c r="D21" t="n">
-        <v>55200</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80000</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="n">
-        <v>123620</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>154.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>145.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>116020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>80000</v>
+        <v>207895</v>
       </c>
       <c r="D23" t="n">
-        <v>31760</v>
+        <v>24598</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25160</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>88000</v>
+        <v>104842</v>
       </c>
       <c r="D24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1431,457 +1431,457 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>120000</v>
+        <v>100737</v>
       </c>
       <c r="D25" t="n">
-        <v>65974</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18050</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160000</v>
+        <v>154842</v>
       </c>
       <c r="D26" t="n">
-        <v>253096</v>
+        <v>12000</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>158.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>35306</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>217790</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80000</v>
+        <v>150737</v>
       </c>
       <c r="D27" t="n">
-        <v>58480</v>
+        <v>66400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13660</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44820</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>144000</v>
+        <v>80000</v>
       </c>
       <c r="D28" t="n">
-        <v>108418</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>83218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>128000</v>
+        <v>80000</v>
       </c>
       <c r="D29" t="n">
-        <v>114818</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>27083</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>87735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>128000</v>
+        <v>108947</v>
       </c>
       <c r="D30" t="n">
-        <v>127040</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>24613.4</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>102426.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>265034</v>
+        <v>10000</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>165.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>84120</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>180914</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="D32" t="n">
-        <v>196958</v>
+        <v>38820</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>25940</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>171018</v>
+        <v>38820</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>高铭瑞</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D33" t="n">
-        <v>111098</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>24780</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>86318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>127858</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>118358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D35" t="n">
-        <v>104150</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>49820</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1893,259 +1893,49 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>104150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>侯晓光</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>96000</v>
+        <v>80000</v>
       </c>
       <c r="D36" t="n">
-        <v>131854</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>137.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>123894</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>陈斌斌</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>104000</v>
-      </c>
-      <c r="D37" t="n">
-        <v>155796</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>149.8%</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>137.4%</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>12940</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>142856</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>丁蕾</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D38" t="n">
-        <v>143720</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>59.9%</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>95508</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>66.5%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>48212</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>梁志超</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D39" t="n">
-        <v>91928</v>
-      </c>
-      <c r="E39" t="n">
-        <v>173964</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>110.8%</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>54073</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>37855</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周紫姻</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8780</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>21.9%</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>91.1%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>李洋洋</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D41" t="n">
-        <v>89038</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>111.3%</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>92.6%</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>14957</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>74081</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -525,31 +525,31 @@
         <v>185200</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>389.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-3699</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>165200</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="5">
@@ -693,19 +693,19 @@
         <v>148350</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="8">
@@ -777,19 +777,19 @@
         <v>207250</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>23898</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>190.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-45600</v>
+        <v>-21702</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>168625</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>168625</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="12">
@@ -987,31 +987,31 @@
         <v>128625</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>50783</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1019.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-45803</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
     </row>
     <row r="17">
@@ -1113,31 +1113,31 @@
         <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>30458</v>
+        <v>47018</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4565</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>30458</v>
+        <v>42453</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>4980</v>
+        <v>15736</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4980</v>
+        <v>15736</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="21">
@@ -1281,27 +1281,27 @@
         <v>95750</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1323,31 +1323,31 @@
         <v>98625</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>207895</v>
       </c>
       <c r="D23" t="n">
-        <v>24598</v>
+        <v>29578</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>24598</v>
+        <v>29578</v>
       </c>
     </row>
     <row r="24">
@@ -1491,19 +1491,19 @@
         <v>154842</v>
       </c>
       <c r="D26" t="n">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="27">
@@ -1549,15 +1549,15 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>66400</v>
+        <v>57400</v>
       </c>
     </row>
     <row r="28">
@@ -1659,19 +1659,19 @@
         <v>108947</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>10000</v>
+        <v>12490</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>10000</v>
+        <v>8490</v>
       </c>
     </row>
     <row r="32">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>191500</v>
       </c>
       <c r="D2" t="n">
-        <v>6774</v>
+        <v>28734</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>8096.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6774</v>
+        <v>20637.3</v>
       </c>
     </row>
     <row r="3">
@@ -567,31 +567,31 @@
         <v>165200</v>
       </c>
       <c r="D4" t="n">
-        <v>19920</v>
+        <v>34860</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>7503</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19920</v>
+        <v>27357</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         <v>98625</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>17319</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>98625</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -751,15 +751,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>207250</v>
       </c>
       <c r="D9" t="n">
-        <v>23898</v>
+        <v>32976</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>45600</v>
+        <v>48916.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>190.8%</t>
+          <t>148.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-21702</v>
+        <v>-15940.67</v>
       </c>
     </row>
     <row r="10">
@@ -987,19 +987,19 @@
         <v>128625</v>
       </c>
       <c r="D14" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1019.7%</t>
+          <t>509.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-45803</v>
+        <v>-40823</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>91500</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>14980</v>
+        <v>19960</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14980</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>47018</v>
+        <v>58696</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>42453</v>
+        <v>54131</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>15736</v>
+        <v>24416</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15736</v>
+        <v>24416</v>
       </c>
     </row>
     <row r="19">
@@ -1239,31 +1239,31 @@
         <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4426.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4980</v>
+        <v>5533.33</v>
       </c>
     </row>
     <row r="21">
@@ -1323,19 +1323,19 @@
         <v>98625</v>
       </c>
       <c r="D22" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4960</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="23">
@@ -1365,31 +1365,31 @@
         <v>207895</v>
       </c>
       <c r="D23" t="n">
-        <v>29578</v>
+        <v>36178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29578</v>
+        <v>31198</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>104842</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>33420</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>33420</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>100737</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="26">
@@ -1701,19 +1701,19 @@
         <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>12490</v>
+        <v>13690</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>8490</v>
+        <v>9690</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>80000</v>
       </c>
       <c r="D32" t="n">
-        <v>38820</v>
+        <v>43800</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>38820</v>
+        <v>43800</v>
       </c>
     </row>
     <row r="33">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>191500</v>
       </c>
       <c r="D2" t="n">
-        <v>28734</v>
+        <v>74994</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8096.7</v>
+        <v>9776.700000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>20637.3</v>
+        <v>65217.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>185200</v>
       </c>
       <c r="D3" t="n">
-        <v>1280</v>
+        <v>6260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>389.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-3699</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="4">
@@ -651,31 +651,31 @@
         <v>98625</v>
       </c>
       <c r="D6" t="n">
-        <v>4980</v>
+        <v>14940</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4000</v>
+        <v>5680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>980</v>
+        <v>9260</v>
       </c>
     </row>
     <row r="7">
@@ -877,15 +877,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>200.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4980</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>148625</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="13">
@@ -1071,19 +1071,19 @@
         <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>19960</v>
+        <v>24940</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19960</v>
+        <v>24940</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>58696</v>
+        <v>84074</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>54131</v>
+        <v>79509</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>24416</v>
+        <v>25696</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>24416</v>
+        <v>25696</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>178900</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>200.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-10000</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5533.33</v>
+        <v>10513.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>95750</v>
       </c>
       <c r="D21" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="22">
@@ -1423,15 +1423,15 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>26820</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>33420</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="25">
@@ -1449,31 +1449,31 @@
         <v>100737</v>
       </c>
       <c r="D25" t="n">
-        <v>24800</v>
+        <v>38000</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>24800</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="26">
@@ -1617,19 +1617,19 @@
         <v>80000</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="30">
@@ -1701,19 +1701,19 @@
         <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>13690</v>
+        <v>24088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9690</v>
+        <v>20088</v>
       </c>
     </row>
     <row r="32">
@@ -1785,19 +1785,19 @@
         <v>80000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>191500</v>
+        <v>312912</v>
       </c>
       <c r="D2" t="n">
         <v>74994</v>
@@ -490,12 +490,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>185200</v>
+        <v>302618</v>
       </c>
       <c r="D3" t="n">
         <v>6260</v>
@@ -532,12 +532,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>165200</v>
+        <v>269938</v>
       </c>
       <c r="D4" t="n">
         <v>34860</v>
@@ -574,12 +574,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98625</v>
+        <v>161154</v>
       </c>
       <c r="D5" t="n">
         <v>22000</v>
@@ -616,12 +616,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>98625</v>
+        <v>161154</v>
       </c>
       <c r="D6" t="n">
         <v>14940</v>
@@ -658,12 +658,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148350</v>
+        <v>242405</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>115750</v>
+        <v>189136</v>
       </c>
       <c r="D8" t="n">
         <v>4980</v>
@@ -742,12 +742,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>207250</v>
+        <v>333616</v>
       </c>
       <c r="D9" t="n">
         <v>32976</v>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>168625</v>
+        <v>271440</v>
       </c>
       <c r="D10" t="n">
         <v>4980</v>
@@ -826,12 +826,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168625</v>
+        <v>271440</v>
       </c>
       <c r="D11" t="n">
         <v>4980</v>
@@ -868,12 +868,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>148625</v>
+        <v>239246</v>
       </c>
       <c r="D12" t="n">
         <v>9960</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>141500</v>
+        <v>227777</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>128625</v>
+        <v>207051</v>
       </c>
       <c r="D14" t="n">
         <v>9960</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>91500</v>
+        <v>147291</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>171500</v>
+        <v>279050</v>
       </c>
       <c r="D16" t="n">
         <v>24940</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>175475</v>
+        <v>285517</v>
       </c>
       <c r="D17" t="n">
         <v>84074</v>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>178625</v>
+        <v>290643</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>178900</v>
+        <v>291091</v>
       </c>
       <c r="D19" t="n">
         <v>4980</v>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>108625</v>
+        <v>176745</v>
       </c>
       <c r="D20" t="n">
         <v>14940</v>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>95750</v>
+        <v>155796</v>
       </c>
       <c r="D21" t="n">
         <v>9960</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>98625</v>
+        <v>160474</v>
       </c>
       <c r="D22" t="n">
         <v>14940</v>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>207895</v>
+        <v>265322</v>
       </c>
       <c r="D23" t="n">
         <v>36178</v>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>104842</v>
+        <v>133802</v>
       </c>
       <c r="D24" t="n">
         <v>33420</v>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100737</v>
+        <v>128563</v>
       </c>
       <c r="D25" t="n">
         <v>38000</v>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>154842</v>
+        <v>197614</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150737</v>
+        <v>192375</v>
       </c>
       <c r="D27" t="n">
         <v>66400</v>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>108947</v>
+        <v>139041</v>
       </c>
       <c r="D30" t="n">
         <v>6600</v>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D31" t="n">
         <v>24088</v>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D33" t="n">
         <v>24800</v>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80000</v>
+        <v>102103</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312912</v>
+        <v>3129120000</v>
       </c>
       <c r="D2" t="n">
         <v>74994</v>
@@ -490,12 +490,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>302618</v>
+        <v>3026180000</v>
       </c>
       <c r="D3" t="n">
         <v>6260</v>
@@ -532,12 +532,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>269938</v>
+        <v>2699380000</v>
       </c>
       <c r="D4" t="n">
         <v>34860</v>
@@ -574,12 +574,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>161154</v>
+        <v>1611540000</v>
       </c>
       <c r="D5" t="n">
         <v>22000</v>
@@ -616,12 +616,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>161154</v>
+        <v>1611540000</v>
       </c>
       <c r="D6" t="n">
         <v>14940</v>
@@ -658,12 +658,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>242405</v>
+        <v>2424050000</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>189136</v>
+        <v>1891360000</v>
       </c>
       <c r="D8" t="n">
         <v>4980</v>
@@ -742,12 +742,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>333616</v>
+        <v>3336160000</v>
       </c>
       <c r="D9" t="n">
         <v>32976</v>
@@ -784,12 +784,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>271440</v>
+        <v>2714400000</v>
       </c>
       <c r="D10" t="n">
         <v>4980</v>
@@ -826,12 +826,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>271440</v>
+        <v>2714400000</v>
       </c>
       <c r="D11" t="n">
         <v>4980</v>
@@ -868,12 +868,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239246</v>
+        <v>2392460000</v>
       </c>
       <c r="D12" t="n">
         <v>9960</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>227777</v>
+        <v>2277770000</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>207051</v>
+        <v>2070510000</v>
       </c>
       <c r="D14" t="n">
         <v>9960</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>147291</v>
+        <v>1472910000</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>279050</v>
+        <v>2790500000</v>
       </c>
       <c r="D16" t="n">
         <v>24940</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>285517</v>
+        <v>2855170000</v>
       </c>
       <c r="D17" t="n">
         <v>84074</v>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>290643</v>
+        <v>2906430000</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>291091</v>
+        <v>2910910000</v>
       </c>
       <c r="D19" t="n">
         <v>4980</v>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>176745</v>
+        <v>1767450000</v>
       </c>
       <c r="D20" t="n">
         <v>14940</v>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155796</v>
+        <v>1557960000</v>
       </c>
       <c r="D21" t="n">
         <v>9960</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>160474</v>
+        <v>1604740000</v>
       </c>
       <c r="D22" t="n">
         <v>14940</v>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>265322</v>
+        <v>2653220000</v>
       </c>
       <c r="D23" t="n">
         <v>36178</v>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>133802</v>
+        <v>1338020000</v>
       </c>
       <c r="D24" t="n">
         <v>33420</v>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>128563</v>
+        <v>1285630000</v>
       </c>
       <c r="D25" t="n">
         <v>38000</v>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197614</v>
+        <v>1976140000</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>192375</v>
+        <v>1923750000</v>
       </c>
       <c r="D27" t="n">
         <v>66400</v>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>139041</v>
+        <v>1390410000</v>
       </c>
       <c r="D30" t="n">
         <v>6600</v>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D31" t="n">
         <v>24088</v>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D33" t="n">
         <v>24800</v>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102103</v>
+        <v>1021030000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,7 +483,7 @@
         <v>3129120000</v>
       </c>
       <c r="D2" t="n">
-        <v>74994</v>
+        <v>84954</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>65217.3</v>
+        <v>75177.3</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>1611540000</v>
       </c>
       <c r="D6" t="n">
-        <v>14940</v>
+        <v>21200</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9260</v>
+        <v>15520</v>
       </c>
     </row>
     <row r="7">
@@ -777,7 +777,7 @@
         <v>3336160000</v>
       </c>
       <c r="D9" t="n">
-        <v>32976</v>
+        <v>42936</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -793,15 +793,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>48916.67</v>
+        <v>53896.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>148.3%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-15940.67</v>
+        <v>-10960.67</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>2714400000</v>
       </c>
       <c r="D10" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -861,7 +861,7 @@
         <v>2714400000</v>
       </c>
       <c r="D11" t="n">
-        <v>4980</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200.8%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-5020</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -903,7 +903,7 @@
         <v>2392460000</v>
       </c>
       <c r="D12" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="13">
@@ -987,7 +987,7 @@
         <v>2070510000</v>
       </c>
       <c r="D14" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1003,11 +1003,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50783</v>
+        <v>55763</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>509.9%</t>
+          <t>373.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1071,7 +1071,7 @@
         <v>2790500000</v>
       </c>
       <c r="D16" t="n">
-        <v>24940</v>
+        <v>34900</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24940</v>
+        <v>34900</v>
       </c>
     </row>
     <row r="17">
@@ -1113,7 +1113,7 @@
         <v>2855170000</v>
       </c>
       <c r="D17" t="n">
-        <v>84074</v>
+        <v>89054</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>79509</v>
+        <v>84489</v>
       </c>
     </row>
     <row r="18">
@@ -1213,15 +1213,15 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10000</v>
+        <v>14980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>200.8%</t>
+          <t>300.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-5020</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="20">
@@ -1239,7 +1239,7 @@
         <v>1767450000</v>
       </c>
       <c r="D20" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10513.33</v>
+        <v>15493.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,7 +1281,7 @@
         <v>1557960000</v>
       </c>
       <c r="D21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="22">
@@ -1323,7 +1323,7 @@
         <v>1604740000</v>
       </c>
       <c r="D22" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1339,11 +1339,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5000</v>
+        <v>9980</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1381,15 +1381,15 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>31198</v>
+        <v>26218</v>
       </c>
     </row>
     <row r="24">
@@ -1449,7 +1449,7 @@
         <v>1285630000</v>
       </c>
       <c r="D25" t="n">
-        <v>38000</v>
+        <v>44600</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1465,15 +1465,15 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2000</v>
+        <v>18800</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>36000</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="26">
@@ -1575,7 +1575,7 @@
         <v>1020980000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="29">
@@ -1659,7 +1659,7 @@
         <v>1390410000</v>
       </c>
       <c r="D30" t="n">
-        <v>6600</v>
+        <v>25200</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6600</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="31">
@@ -1785,7 +1785,7 @@
         <v>1020980000</v>
       </c>
       <c r="D33" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3129120000</v>
+        <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>84954</v>
+        <v>75177.3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3026180000</v>
+        <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>6260</v>
+        <v>1281</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2699380000</v>
+        <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>34860</v>
+        <v>27357</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1611540000</v>
+        <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>22000</v>
+        <v>17319</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1611540000</v>
+        <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>21200</v>
+        <v>15520</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2424050000</v>
+        <v>242405</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -700,12 +700,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1891360000</v>
+        <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3336160000</v>
+        <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>42936</v>
+        <v>-10960.67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2714400000</v>
+        <v>271440</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -858,22 +858,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2714400000</v>
+        <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>10160</v>
+        <v>160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2392460000</v>
+        <v>239246</v>
       </c>
       <c r="D12" t="n">
         <v>14940</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2277770000</v>
+        <v>227777</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2070510000</v>
+        <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>14940</v>
+        <v>-40823</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1472910000</v>
+        <v>147291</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2790500000</v>
+        <v>279050</v>
       </c>
       <c r="D16" t="n">
         <v>34900</v>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1110,22 +1110,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2855170000</v>
+        <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>89054</v>
+        <v>84489</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2906430000</v>
+        <v>290643</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1194,22 +1194,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2910910000</v>
+        <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>4980</v>
+        <v>-10000</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1767450000</v>
+        <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>19920</v>
+        <v>15493.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1557960000</v>
+        <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>14940</v>
+        <v>9960</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1604740000</v>
+        <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>19920</v>
+        <v>9940</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1362,22 +1362,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2653220000</v>
+        <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>36178</v>
+        <v>26218</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1338020000</v>
+        <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>33420</v>
+        <v>6600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1446,22 +1446,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1285630000</v>
+        <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>44600</v>
+        <v>25800</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1976140000</v>
+        <v>197614</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1530,22 +1530,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1923750000</v>
+        <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>66400</v>
+        <v>57400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D28" t="n">
         <v>6600</v>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1390410000</v>
+        <v>139041</v>
       </c>
       <c r="D30" t="n">
         <v>25200</v>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>24088</v>
+        <v>20088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D33" t="n">
         <v>34800</v>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1021030000</v>
+        <v>102103</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>75177.3</v>
+        <v>84954</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>1281</v>
+        <v>6260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>27357</v>
+        <v>34860</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>17319</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>15520</v>
+        <v>21200</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>-10960.67</v>
+        <v>42936</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>-40823</v>
+        <v>14940</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>84489</v>
+        <v>89054</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>-10000</v>
+        <v>4980</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>15493.33</v>
+        <v>19920</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>9940</v>
+        <v>19920</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>26218</v>
+        <v>36178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>6600</v>
+        <v>33420</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>25800</v>
+        <v>44600</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>57400</v>
+        <v>66400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>20088</v>
+        <v>24088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H31" t="n">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>84954</v>
+        <v>80372</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9776.700000000001</v>
+        <v>13491.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>75177.3</v>
+        <v>66880.3</v>
       </c>
     </row>
     <row r="3">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>34860</v>
+        <v>44820</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>27357</v>
+        <v>37317</v>
       </c>
     </row>
     <row r="5">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>21200</v>
+        <v>24900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>15520</v>
+        <v>19220</v>
       </c>
     </row>
     <row r="7">
@@ -751,15 +751,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3980</v>
+        <v>10580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>212.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1000</v>
+        <v>-5600</v>
       </c>
     </row>
     <row r="9">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1792</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-1792</v>
       </c>
     </row>
     <row r="11">
@@ -877,15 +877,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10000</v>
+        <v>14150</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>139.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>160</v>
+        <v>-3990</v>
       </c>
     </row>
     <row r="12">
@@ -987,31 +987,31 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55763</v>
+        <v>57263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>373.2%</t>
+          <t>287.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-40823</v>
+        <v>-37343</v>
       </c>
     </row>
     <row r="15">
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>25696</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>300.8%</t>
+          <t>150.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-10000</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>19920</v>
+        <v>14940</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15493.33</v>
+        <v>10513.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="22">
@@ -1339,15 +1339,15 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9980</v>
+        <v>19980</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9940</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>36178</v>
+        <v>55978</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>26218</v>
+        <v>46018</v>
       </c>
     </row>
     <row r="24">
@@ -1449,31 +1449,31 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>44600</v>
+        <v>45396</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18800</v>
+        <v>32000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>25800</v>
+        <v>13396</v>
       </c>
     </row>
     <row r="26">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>6600</v>
+        <v>16600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6600</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="29">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>34800</v>
+        <v>41400</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>34800</v>
+        <v>41400</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>80372</v>
+        <v>93333</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>66880.3</v>
+        <v>79841.3</v>
       </c>
     </row>
     <row r="3">
@@ -751,15 +751,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10580</v>
+        <v>14560</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>212.4%</t>
+          <t>292.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-5600</v>
+        <v>-9580</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>42936</v>
+        <v>47916</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>53896.67</v>
+        <v>73696.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>153.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-10960.67</v>
+        <v>-25780.67</v>
       </c>
     </row>
     <row r="10">
@@ -877,15 +877,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14150</v>
+        <v>17466.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>139.3%</t>
+          <t>171.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-3990</v>
+        <v>-7306.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>34900</v>
+        <v>73720</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>34900</v>
+        <v>73720</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>89054</v>
+        <v>92854</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>84489</v>
+        <v>88289</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>25696</v>
+        <v>35696</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>896</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="19">
@@ -1239,31 +1239,31 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>14940</v>
+        <v>21540</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4426.67</v>
+        <v>4626.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10513.33</v>
+        <v>16913.33</v>
       </c>
     </row>
     <row r="21">
@@ -1365,31 +1365,31 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>55978</v>
+        <v>74158</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>46018</v>
+        <v>59218</v>
       </c>
     </row>
     <row r="24">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>66400</v>
+        <v>106000</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>57400</v>
+        <v>97000</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>16600</v>
+        <v>36600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>16600</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="29">
@@ -1659,31 +1659,31 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>25200</v>
+        <v>25598</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25200</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="31">
@@ -1717,15 +1717,15 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4000</v>
+        <v>11500</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>20088</v>
+        <v>12588</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>43800</v>
+        <v>53800</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>43800</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="33">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>93333</v>
+        <v>108273</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>79841.3</v>
+        <v>94781.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>6260</v>
+        <v>32660</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1281</v>
+        <v>27681</v>
       </c>
     </row>
     <row r="4">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>7410</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>158.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4681</v>
+        <v>-2729</v>
       </c>
     </row>
     <row r="8">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1792</v>
+        <v>11752</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-1792</v>
+        <v>-11752</v>
       </c>
     </row>
     <row r="11">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>6600</v>
+        <v>11580</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6600</v>
+        <v>11580</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>73720</v>
+        <v>93520</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>73720</v>
+        <v>93520</v>
       </c>
     </row>
     <row r="17">
@@ -1129,15 +1129,15 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4565</v>
+        <v>9545</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>88289</v>
+        <v>83309</v>
       </c>
     </row>
     <row r="18">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>21540</v>
+        <v>26520</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16913.33</v>
+        <v>21893.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>19920</v>
+        <v>20420</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14940</v>
+        <v>15440</v>
       </c>
     </row>
     <row r="22">
@@ -1339,15 +1339,15 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19980</v>
+        <v>23629</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100.3%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-60</v>
+        <v>-3709</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>74158</v>
+        <v>87178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>59218</v>
+        <v>72238</v>
       </c>
     </row>
     <row r="24">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>45396</v>
+        <v>84996</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13396</v>
+        <v>52996</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>24000</v>
+        <v>30820</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>24000</v>
+        <v>30820</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>106000</v>
+        <v>107680</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>97000</v>
+        <v>98680</v>
       </c>
     </row>
     <row r="28">
@@ -1575,31 +1575,31 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>36600</v>
+        <v>61320</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>36600</v>
+        <v>55820</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>12000</v>
+        <v>50820</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>12000</v>
+        <v>50420</v>
       </c>
     </row>
     <row r="30">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>24088</v>
+        <v>37288</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12588</v>
+        <v>25788</v>
       </c>
     </row>
     <row r="32">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-24800</v>
       </c>
     </row>
     <row r="36">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>108273</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13491.7</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>94781.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>32660</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4979</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>27681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -567,31 +567,31 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>44820</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7503</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>37317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4681</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>24900</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5680</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -693,31 +693,31 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>4681</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7410</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>158.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-2729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -735,31 +735,31 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14560</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>292.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-9580</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>47916</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>73696.67</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>153.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-25780.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11752</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-11752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -861,31 +861,31 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>10160</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>17466.7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>171.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-7306.700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>14940</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14940</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -987,31 +987,31 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>19920</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>57263</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>287.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-37343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>11580</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11580</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>93520</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>93520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1113,31 +1113,31 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>92854</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9545</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>83309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1155,31 +1155,31 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>35696</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1197,31 +1197,31 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>150.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-5020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1239,31 +1239,31 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>26520</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4626.67</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21893.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1281,31 +1281,31 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>20420</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1323,31 +1323,31 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>19920</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>23629</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-3709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1365,31 +1365,31 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>87178</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14940</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>72238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1407,31 +1407,31 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>33420</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>26820</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1449,31 +1449,31 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>84996</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>52996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>30820</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30820</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1533,31 +1533,31 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>107680</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>98680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1575,31 +1575,31 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>61320</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>55820</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>50820</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>50420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1659,31 +1659,31 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>25598</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>24598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1701,31 +1701,31 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>37288</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>11500</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>25788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>53800</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>53800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>41400</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>41400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-24800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>13491.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-13491.7</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-4979</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>7503</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-7503</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-4681</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-5680</v>
       </c>
     </row>
     <row r="7">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>7410</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-7410</v>
       </c>
     </row>
     <row r="8">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-14560</v>
       </c>
     </row>
     <row r="9">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>73696.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-73696.67</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>11752</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-11752</v>
       </c>
     </row>
     <row r="11">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>17466.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-17466.7</v>
       </c>
     </row>
     <row r="12">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>57263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-57263</v>
       </c>
     </row>
     <row r="15">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>9545</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-9545</v>
       </c>
     </row>
     <row r="18">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-24800</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-14980</v>
       </c>
     </row>
     <row r="20">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4626.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-4626.67</v>
       </c>
     </row>
     <row r="21">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-4980</v>
       </c>
     </row>
     <row r="22">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>23629</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-23629</v>
       </c>
     </row>
     <row r="23">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-14940</v>
       </c>
     </row>
     <row r="24">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>26820</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-26820</v>
       </c>
     </row>
     <row r="25">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
     </row>
     <row r="26">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
     </row>
     <row r="28">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-5500</v>
       </c>
     </row>
     <row r="29">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="30">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="31">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-11500</v>
       </c>
     </row>
     <row r="32">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-24800</v>
       </c>
     </row>
     <row r="36">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>108273</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-13491.7</v>
+        <v>94781.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>32660</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-4979</v>
+        <v>27681</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>44820</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-7503</v>
+        <v>37317</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-4681</v>
+        <v>17319</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-5680</v>
+        <v>19220</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>158.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-7410</v>
+        <v>-2729</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>292.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-14560</v>
+        <v>-9580</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>47916</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>153.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-73696.67</v>
+        <v>-25780.67</v>
       </c>
     </row>
     <row r="10">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>171.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-17466.7</v>
+        <v>-7306.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>287.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-57263</v>
+        <v>-37343</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>93520</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>93520</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>92854</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-9545</v>
+        <v>83309</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>35696</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-24800</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>150.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-14980</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26520</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-4626.67</v>
+        <v>21893.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>20420</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-4980</v>
+        <v>15440</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-23629</v>
+        <v>-3709</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>87178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-14940</v>
+        <v>72238</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>33420</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-26820</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>84996</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-32000</v>
+        <v>52996</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>30820</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>30820</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>107680</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-9000</v>
+        <v>98680</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>61320</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-5500</v>
+        <v>55820</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>50820</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>-400</v>
+        <v>50420</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>25598</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-1000</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>37288</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>-11500</v>
+        <v>25788</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>53800</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>41400</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>41400</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>108273</v>
+        <v>113253</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>94781.3</v>
+        <v>99761.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>32660</v>
+        <v>42620</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>27681</v>
+        <v>37641</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>44820</v>
+        <v>91020</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>37317</v>
+        <v>83517</v>
       </c>
     </row>
     <row r="5">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>4681</v>
+        <v>11281</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>158.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-2729</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="8">
@@ -819,31 +819,31 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11752</v>
+        <v>13344</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>134.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-11752</v>
+        <v>-3384</v>
       </c>
     </row>
     <row r="11">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>14940</v>
+        <v>39720</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14940</v>
+        <v>39720</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>19920</v>
+        <v>20518</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>287.5%</t>
+          <t>279.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-37343</v>
+        <v>-36745</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>11580</v>
+        <v>17840</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11580</v>
+        <v>17840</v>
       </c>
     </row>
     <row r="16">
@@ -1071,31 +1071,31 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>93520</v>
+        <v>142120</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>93520</v>
+        <v>138140</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>92854</v>
+        <v>105344</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>83309</v>
+        <v>95799</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>35696</v>
+        <v>45656</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10896</v>
+        <v>20856</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>9960</v>
+        <v>16220</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>150.4%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-5020</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>26520</v>
+        <v>38100</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21893.33</v>
+        <v>33473.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>20420</v>
+        <v>25400</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15440</v>
+        <v>20420</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>19920</v>
+        <v>30318</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-3709</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="23">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>33420</v>
+        <v>46620</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6600</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>84996</v>
+        <v>123808</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>52996</v>
+        <v>91808</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>30820</v>
+        <v>55800</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30820</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>107680</v>
+        <v>127480</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>98680</v>
+        <v>118480</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>61320</v>
+        <v>87040</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>55820</v>
+        <v>81540</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>50820</v>
+        <v>70620</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>50420</v>
+        <v>70220</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>25598</v>
+        <v>70598</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>24598</v>
+        <v>69598</v>
       </c>
     </row>
     <row r="31">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>53800</v>
+        <v>73600</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>53800</v>
+        <v>73600</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>41400</v>
+        <v>48000</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>41400</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>113253</v>
+        <v>24900</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>99761.3</v>
+        <v>11408.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>42620</v>
+        <v>41340</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>37641</v>
+        <v>36361</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>91020</v>
+        <v>46200</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>83517</v>
+        <v>38697</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17319</v>
+        <v>-4681</v>
       </c>
     </row>
     <row r="6">
@@ -651,31 +651,31 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>24900</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5680</v>
+        <v>8170</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19220</v>
+        <v>-8170</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>11281</v>
+        <v>7880</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3871</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>292.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-9580</v>
+        <v>-14560</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>47916</v>
+        <v>19920</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>73696.67</v>
+        <v>77013.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>153.8%</t>
+          <t>386.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-25780.67</v>
+        <v>-57093.37</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-3384</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>10160</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>171.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-7306.700000000001</v>
+        <v>-17466.7</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>39720</v>
+        <v>29760</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>39720</v>
+        <v>29760</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>20518</v>
+        <v>10558</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>279.1%</t>
+          <t>542.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-36745</v>
+        <v>-46705</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>17840</v>
+        <v>16220</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17840</v>
+        <v>16220</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>142120</v>
+        <v>70200</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>138140</v>
+        <v>66220</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>105344</v>
+        <v>22450</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>95799</v>
+        <v>12905</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>45656</v>
+        <v>14940</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>166.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>20856</v>
+        <v>-9860</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>16220</v>
+        <v>31160</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1240</v>
+        <v>16180</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>38100</v>
+        <v>21540</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>33473.33</v>
+        <v>16913.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>25400</v>
+        <v>24120</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>20420</v>
+        <v>19140</v>
       </c>
     </row>
     <row r="22">
@@ -1323,31 +1323,31 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>30318</v>
+        <v>25776</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>23629</v>
+        <v>33629</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>130.5%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6689</v>
+        <v>-7853</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>87178</v>
+        <v>13020</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>72238</v>
+        <v>-1920</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>46620</v>
+        <v>52800</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>19800</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>123808</v>
+        <v>78912</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>91808</v>
+        <v>46912</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>55800</v>
+        <v>31800</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>55800</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="27">
@@ -1533,31 +1533,31 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>127480</v>
+        <v>41280</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9000</v>
+        <v>27700</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>118480</v>
+        <v>13580</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>87040</v>
+        <v>130040</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>81540</v>
+        <v>124540</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>70620</v>
+        <v>58620</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>400</v>
+        <v>7000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>70220</v>
+        <v>51620</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>70598</v>
+        <v>45000</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>69598</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>37288</v>
+        <v>49600</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>25788</v>
+        <v>38100</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>73600</v>
+        <v>33000</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>73600</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>48000</v>
+        <v>26400</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>48000</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>24900</v>
+        <v>118233</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11408.3</v>
+        <v>104741.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>41340</v>
+        <v>47600</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>36361</v>
+        <v>42621</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>46200</v>
+        <v>91020</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>38697</v>
+        <v>83517</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-4681</v>
+        <v>17319</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-8170</v>
+        <v>16730</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>7880</v>
+        <v>12561</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>470</v>
+        <v>5151</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>292.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-14560</v>
+        <v>-9580</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>19920</v>
+        <v>67836</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>386.6%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-57093.37</v>
+        <v>-9177.369999999995</v>
       </c>
     </row>
     <row r="10">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>171.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-17466.7</v>
+        <v>-7306.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>29760</v>
+        <v>44700</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29760</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>10558</v>
+        <v>29880</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>542.4%</t>
+          <t>191.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-46705</v>
+        <v>-27383</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>16220</v>
+        <v>22820</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16220</v>
+        <v>22820</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>70200</v>
+        <v>143920</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>66220</v>
+        <v>139940</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>22450</v>
+        <v>115304</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>12905</v>
+        <v>105759</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>14940</v>
+        <v>50636</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>166.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-9860</v>
+        <v>25836</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>31160</v>
+        <v>41120</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16180</v>
+        <v>26140</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>21540</v>
+        <v>38100</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16913.33</v>
+        <v>33473.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>24120</v>
+        <v>44040</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19140</v>
+        <v>39060</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>25776</v>
+        <v>45696</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>130.5%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-7853</v>
+        <v>12067</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>13020</v>
+        <v>87178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-1920</v>
+        <v>72238</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>52800</v>
+        <v>86220</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>25980</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>78912</v>
+        <v>124308</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>46912</v>
+        <v>92308</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>31800</v>
+        <v>55800</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>31800</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>41280</v>
+        <v>147280</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>13580</v>
+        <v>119580</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>130040</v>
+        <v>166640</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>163.2%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>163.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>124540</v>
+        <v>161140</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>58620</v>
+        <v>70620</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>51620</v>
+        <v>63620</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>45000</v>
+        <v>70598</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>44000</v>
+        <v>69598</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>49600</v>
+        <v>80288</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>38100</v>
+        <v>68788</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>33000</v>
+        <v>86800</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>33000</v>
+        <v>86800</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>26400</v>
+        <v>67800</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>26400</v>
+        <v>67800</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>118233</v>
+        <v>123213</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13491.7</v>
+        <v>20091.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>104741.3</v>
+        <v>103121.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>47600</v>
+        <v>57560</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4979</v>
+        <v>9959</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>42621</v>
+        <v>47601</v>
       </c>
     </row>
     <row r="4">
@@ -819,31 +819,31 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>14940</v>
+        <v>9960</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13344</v>
+        <v>18324</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>184.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1596</v>
+        <v>-8364</v>
       </c>
     </row>
     <row r="11">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3980</v>
+        <v>35780</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>139940</v>
+        <v>108140</v>
       </c>
     </row>
     <row r="17">
@@ -1113,23 +1113,23 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>115304</v>
+        <v>120284</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9545</v>
+        <v>9943</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>105759</v>
+        <v>110341</v>
       </c>
     </row>
     <row r="18">
@@ -1155,31 +1155,31 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>50636</v>
+        <v>45656</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>24800</v>
+        <v>29780</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>25836</v>
+        <v>15876</v>
       </c>
     </row>
     <row r="19">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>38100</v>
+        <v>36480</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>33473.33</v>
+        <v>31853.33</v>
       </c>
     </row>
     <row r="21">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>45696</v>
+        <v>50676</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>12067</v>
+        <v>17047</v>
       </c>
     </row>
     <row r="23">
@@ -1381,15 +1381,15 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>72238</v>
+        <v>67258</v>
       </c>
     </row>
     <row r="24">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>124308</v>
+        <v>158296</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>92308</v>
+        <v>126296</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>55800</v>
+        <v>30820</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>55800</v>
+        <v>30820</v>
       </c>
     </row>
     <row r="27">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>166640</v>
+        <v>121920</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>163.2%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>163.2%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>161140</v>
+        <v>116420</v>
       </c>
     </row>
     <row r="29">
@@ -1633,15 +1633,15 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>63620</v>
+        <v>57620</v>
       </c>
     </row>
     <row r="30">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>86800</v>
+        <v>93400</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>86800</v>
+        <v>93400</v>
       </c>
     </row>
     <row r="33">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>123213</v>
+        <v>135191</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>20091.7</v>
+        <v>28591.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>103121.3</v>
+        <v>106599.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>57560</v>
+        <v>77878</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9959</v>
+        <v>14939</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>47601</v>
+        <v>62939</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>91020</v>
+        <v>92700</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>83517</v>
+        <v>85197</v>
       </c>
     </row>
     <row r="5">
@@ -667,15 +667,15 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8170</v>
+        <v>10870</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16730</v>
+        <v>14030</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>12561</v>
+        <v>34561</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5151</v>
+        <v>27151</v>
       </c>
     </row>
     <row r="8">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>67836</v>
+        <v>82776</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>77013.37</v>
+        <v>101813.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-9177.369999999995</v>
+        <v>-19037.37</v>
       </c>
     </row>
     <row r="10">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>44700</v>
+        <v>49680</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44700</v>
+        <v>49680</v>
       </c>
     </row>
     <row r="13">
@@ -1003,15 +1003,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>57263</v>
+        <v>63863</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>191.6%</t>
+          <t>213.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-27383</v>
+        <v>-33983</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>22820</v>
+        <v>27830</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22820</v>
+        <v>27830</v>
       </c>
     </row>
     <row r="16">
@@ -1071,31 +1071,31 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>143920</v>
+        <v>149298</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>35780</v>
+        <v>40760</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>108140</v>
+        <v>108538</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>120284</v>
+        <v>123984</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>110341</v>
+        <v>114041</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>45656</v>
+        <v>57236</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15876</v>
+        <v>27456</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>41120</v>
+        <v>41718</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>26140</v>
+        <v>26738</v>
       </c>
     </row>
     <row r="20">
@@ -1239,31 +1239,31 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>36480</v>
+        <v>53179</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4626.67</v>
+        <v>8606.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31853.33</v>
+        <v>44572.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>44040</v>
+        <v>54000</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39060</v>
+        <v>49020</v>
       </c>
     </row>
     <row r="22">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>87178</v>
+        <v>126778</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>67258</v>
+        <v>106858</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>86220</v>
+        <v>96618</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>59400</v>
+        <v>69798</v>
       </c>
     </row>
     <row r="25">
@@ -1465,15 +1465,15 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>32000</v>
+        <v>40280</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>126296</v>
+        <v>118016</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>30820</v>
+        <v>102200</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30820</v>
+        <v>102200</v>
       </c>
     </row>
     <row r="27">
@@ -1549,15 +1549,15 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>27700</v>
+        <v>34300</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>119580</v>
+        <v>112980</v>
       </c>
     </row>
     <row r="28">
@@ -1575,31 +1575,31 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>121920</v>
+        <v>129640</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5500</v>
+        <v>22300</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>116420</v>
+        <v>107340</v>
       </c>
     </row>
     <row r="29">
@@ -1659,31 +1659,31 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>70598</v>
+        <v>104798</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>69598</v>
+        <v>98798</v>
       </c>
     </row>
     <row r="31">
@@ -1717,15 +1717,15 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>11500</v>
+        <v>21300</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>68788</v>
+        <v>58988</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>93400</v>
+        <v>113200</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>93400</v>
+        <v>113200</v>
       </c>
     </row>
     <row r="33">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>24800</v>
+        <v>28300</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-24800</v>
+        <v>-28300</v>
       </c>
     </row>
     <row r="36">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>135191</v>
+        <v>130211</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>106599.3</v>
+        <v>101619.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>77878</v>
+        <v>174130</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14939</v>
+        <v>24899</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>62939</v>
+        <v>149231</v>
       </c>
     </row>
     <row r="4">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>45856</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>292.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-9580</v>
+        <v>31296</v>
       </c>
     </row>
     <row r="9">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>27830</v>
+        <v>32810</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>27830</v>
+        <v>32810</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>149298</v>
+        <v>159656</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>108538</v>
+        <v>118896</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>123984</v>
+        <v>148884</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>114041</v>
+        <v>138941</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>57236</v>
+        <v>118616</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>27456</v>
+        <v>88836</v>
       </c>
     </row>
     <row r="19">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>53179</v>
+        <v>107660</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>44572.33</v>
+        <v>99053.33</v>
       </c>
     </row>
     <row r="21">
@@ -1936,6 +1936,342 @@
       </c>
       <c r="J36" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>姚闯</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>58216</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>29.1%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>29.1%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>31780</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>54.6%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>26436</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>魏恺志</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4320</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1980</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>杨旺忠</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>73840</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>29.5%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>29.5%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>4060</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>69780</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>闫浩</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>余文静</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>33520</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>13.4%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>3960</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>29560</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>陈鑫</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>309090</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1980</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>307110</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>吴云龙</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>57280</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>57280</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>龙刚</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2080</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2980</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>143.3%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>-900</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>130211</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>101619.3</v>
+        <v>-28591.7</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>174130</v>
+        <v>4980</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>149231</v>
+        <v>-19919</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>92700</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>85197</v>
+        <v>-7503</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17319</v>
+        <v>-4681</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>24900</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14030</v>
+        <v>-10870</v>
       </c>
     </row>
     <row r="7">
@@ -693,31 +693,31 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>34561</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7410</v>
+        <v>12390</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>27151</v>
+        <v>-12390</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>45856</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>31296</v>
+        <v>-14560</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>82776</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-19037.37</v>
+        <v>-101813.37</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>184.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-8364</v>
+        <v>-18324</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>10160</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>171.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-7306.700000000001</v>
+        <v>-17466.7</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>49680</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>49680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>29880</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>213.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-33983</v>
+        <v>-63863</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>32810</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>32810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>159656</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>118896</v>
+        <v>-40760</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>148884</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>138941</v>
+        <v>-9943</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>118616</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>88836</v>
+        <v>-29780</v>
       </c>
     </row>
     <row r="19">
@@ -1197,31 +1197,31 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>41718</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14980</v>
+        <v>18780</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>26738</v>
+        <v>-18780</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>107660</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>99053.33</v>
+        <v>-8606.67</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>54000</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>49020</v>
+        <v>-4980</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>50676</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17047</v>
+        <v>-33629</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>126778</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>106858</v>
+        <v>-19920</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>96618</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>69798</v>
+        <v>-26820</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>158296</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>118016</v>
+        <v>-40280</v>
       </c>
     </row>
     <row r="26">
@@ -1491,19 +1491,19 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>102200</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>102200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>147280</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>112980</v>
+        <v>-34300</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>129640</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>107340</v>
+        <v>-22300</v>
       </c>
     </row>
     <row r="29">
@@ -1617,31 +1617,31 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>70620</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13000</v>
+        <v>23000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>57620</v>
+        <v>-23000</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>104798</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>98798</v>
+        <v>-6000</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>80288</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>58988</v>
+        <v>-21300</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>113200</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>113200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>67800</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>67800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1953,19 +1953,19 @@
         <v>200000</v>
       </c>
       <c r="D37" t="n">
-        <v>58216</v>
+        <v>1980</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>1605.1%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>26436</v>
+        <v>-29800</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>100000</v>
       </c>
       <c r="D38" t="n">
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2340</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>73840</v>
+        <v>280</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>1450.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>69780</v>
+        <v>-3780</v>
       </c>
     </row>
     <row r="40">
@@ -2121,19 +2121,19 @@
         <v>250000</v>
       </c>
       <c r="D41" t="n">
-        <v>33520</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>29560</v>
+        <v>-3960</v>
       </c>
     </row>
     <row r="42">
@@ -2163,19 +2163,19 @@
         <v>400000</v>
       </c>
       <c r="D42" t="n">
-        <v>309090</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>307110</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="43">
@@ -2205,19 +2205,19 @@
         <v>200000</v>
       </c>
       <c r="D43" t="n">
-        <v>57280</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>57280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2247,19 +2247,19 @@
         <v>100000</v>
       </c>
       <c r="D44" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>143.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-900</v>
+        <v>-2980</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>150131</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-28591.7</v>
+        <v>121539.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>4980</v>
+        <v>208990</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-19919</v>
+        <v>184091</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>122580</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-7503</v>
+        <v>115077</v>
       </c>
     </row>
     <row r="5">
@@ -609,19 +609,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -629,11 +629,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-4681</v>
+        <v>17319</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>29880</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-10870</v>
+        <v>19010</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>49501</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-12390</v>
+        <v>37111</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>65776</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-14560</v>
+        <v>51216</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>87756</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-101813.37</v>
+        <v>-14057.37</v>
       </c>
     </row>
     <row r="10">
@@ -819,19 +819,19 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>184.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-18324</v>
+        <v>-8364</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-17466.7</v>
+        <v>7633.299999999999</v>
       </c>
     </row>
     <row r="12">
@@ -903,31 +903,31 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>59640</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>24.9%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>24.9%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>59640</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>36480</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>175.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-63863</v>
+        <v>-27383</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>32810</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>32810</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>174596</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>-40760</v>
+        <v>133836</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>160884</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-9943</v>
+        <v>150941</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>128576</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-29780</v>
+        <v>98796</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>51678</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-18780</v>
+        <v>32898</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>112640</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-8606.67</v>
+        <v>104033.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-4980</v>
+        <v>49020</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>70636</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-33629</v>
+        <v>37007</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>128758</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-19920</v>
+        <v>108838</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1407,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>96618</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1427,11 +1427,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-26820</v>
+        <v>69798</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>178096</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>138.5%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>138.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-40280</v>
+        <v>137816</v>
       </c>
     </row>
     <row r="26">
@@ -1491,31 +1491,31 @@
         <v>197614</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>102200</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>102200</v>
       </c>
     </row>
     <row r="27">
@@ -1533,19 +1533,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147280</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1553,11 +1553,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-34300</v>
+        <v>112980</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>129640</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-22300</v>
+        <v>107340</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>70620</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>-23000</v>
+        <v>47620</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>104798</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-6000</v>
+        <v>98798</v>
       </c>
     </row>
     <row r="31">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>80288</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>-21300</v>
+        <v>58988</v>
       </c>
     </row>
     <row r="32">
@@ -1743,31 +1743,31 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>113200</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>110.9%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>110.9%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>113200</v>
       </c>
     </row>
     <row r="33">
@@ -1785,31 +1785,31 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>92620</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>90.7%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>90.7%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>92620</v>
       </c>
     </row>
     <row r="34">
@@ -1953,19 +1953,19 @@
         <v>200000</v>
       </c>
       <c r="D37" t="n">
-        <v>1980</v>
+        <v>58614</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1605.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>-29800</v>
+        <v>26834</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>100000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-1980</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>280</v>
+        <v>73840</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1450.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>-3780</v>
+        <v>69780</v>
       </c>
     </row>
     <row r="40">
@@ -2121,19 +2121,19 @@
         <v>250000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>34600</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-3960</v>
+        <v>30640</v>
       </c>
     </row>
     <row r="42">
@@ -2163,19 +2163,19 @@
         <v>400000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>355950</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>-1980</v>
+        <v>353970</v>
       </c>
     </row>
     <row r="43">
@@ -2205,31 +2205,31 @@
         <v>200000</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>57280</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>57280</v>
       </c>
     </row>
     <row r="44">
@@ -2247,19 +2247,19 @@
         <v>100000</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>143.3%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-2980</v>
+        <v>-900</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>目标(元)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>完成(元)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>本月退费</t>
+          <t>本月退费(元)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>本月净流水</t>
+          <t>本月净流水(元)</t>
         </is>
       </c>
     </row>
@@ -483,19 +483,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>150131</v>
+        <v>160091</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -503,11 +503,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>121539.3</v>
+        <v>131499.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>208990</v>
+        <v>250508</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>24899</v>
+        <v>28215.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>184091</v>
+        <v>222292.3</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>122580</v>
+        <v>132540</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>115077</v>
+        <v>125037</v>
       </c>
     </row>
     <row r="5">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>29880</v>
+        <v>44820</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19010</v>
+        <v>33950</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>49501</v>
+        <v>54481</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>37111</v>
+        <v>42091</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>65776</v>
+        <v>74456</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>51216</v>
+        <v>59896</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>87756</v>
+        <v>107556</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>101813.37</v>
+        <v>126613.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-14057.37</v>
+        <v>-19057.37</v>
       </c>
     </row>
     <row r="10">
@@ -861,31 +861,31 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>25100</v>
+        <v>31700</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>17466.7</v>
+        <v>22446.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7633.299999999999</v>
+        <v>9253.299999999999</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>59640</v>
+        <v>79560</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>59640</v>
+        <v>79560</v>
       </c>
     </row>
     <row r="13">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>32810</v>
+        <v>37790</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>32810</v>
+        <v>37790</v>
       </c>
     </row>
     <row r="16">
@@ -1071,31 +1071,31 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>174596</v>
+        <v>214396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>40760</v>
+        <v>44760</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>133836</v>
+        <v>169636</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>160884</v>
+        <v>172862</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>150941</v>
+        <v>162919</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>128576</v>
+        <v>147174</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>98796</v>
+        <v>117394</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>51678</v>
+        <v>62036</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32898</v>
+        <v>43256</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>112640</v>
+        <v>119620</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>104033.33</v>
+        <v>111013.33</v>
       </c>
     </row>
     <row r="21">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>128758</v>
+        <v>141132</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>108838</v>
+        <v>121212</v>
       </c>
     </row>
     <row r="24">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>70620</v>
+        <v>77220</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>47620</v>
+        <v>54220</v>
       </c>
     </row>
     <row r="30">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>80288</v>
+        <v>82778</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>58988</v>
+        <v>61478</v>
       </c>
     </row>
     <row r="32">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>113200</v>
+        <v>133000</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>113200</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="33">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>92620</v>
+        <v>106418</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>92620</v>
+        <v>106418</v>
       </c>
     </row>
     <row r="34">
@@ -1953,19 +1953,19 @@
         <v>200000</v>
       </c>
       <c r="D37" t="n">
-        <v>58614</v>
+        <v>58894</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>26834</v>
+        <v>27114</v>
       </c>
     </row>
     <row r="38">
@@ -1995,19 +1995,19 @@
         <v>100000</v>
       </c>
       <c r="D38" t="n">
-        <v>6300</v>
+        <v>8280</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4320</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="39">
@@ -2121,19 +2121,19 @@
         <v>250000</v>
       </c>
       <c r="D41" t="n">
-        <v>34600</v>
+        <v>36980</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2141,11 +2141,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>30640</v>
+        <v>33020</v>
       </c>
     </row>
     <row r="42">
@@ -2163,19 +2163,19 @@
         <v>400000</v>
       </c>
       <c r="D42" t="n">
-        <v>355950</v>
+        <v>312150</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>353970</v>
+        <v>310170</v>
       </c>
     </row>
     <row r="43">
@@ -2247,19 +2247,19 @@
         <v>100000</v>
       </c>
       <c r="D44" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>143.3%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-900</v>
+        <v>-790</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>250508</v>
+        <v>280288</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>222292.3</v>
+        <v>252072.3</v>
       </c>
     </row>
     <row r="4">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>44820</v>
+        <v>45218</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33950</v>
+        <v>34348</v>
       </c>
     </row>
     <row r="7">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>74456</v>
+        <v>79436</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59896</v>
+        <v>64876</v>
       </c>
     </row>
     <row r="9">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>36480</v>
+        <v>36878</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>175.1%</t>
+          <t>173.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-27383</v>
+        <v>-26985</v>
       </c>
     </row>
     <row r="15">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>119620</v>
+        <v>144420</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>111013.33</v>
+        <v>135813.33</v>
       </c>
     </row>
     <row r="21">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>70636</v>
+        <v>87436</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>37007</v>
+        <v>53807</v>
       </c>
     </row>
     <row r="23">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>178096</v>
+        <v>198096</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>154.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>154.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>137816</v>
+        <v>157816</v>
       </c>
     </row>
     <row r="26">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>106418</v>
+        <v>116418</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>106418</v>
+        <v>116418</v>
       </c>
     </row>
     <row r="34">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>160091</v>
+        <v>165469</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>28591.7</v>
+        <v>35561.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>131499.3</v>
+        <v>129907.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>280288</v>
+        <v>310168</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>252072.3</v>
+        <v>281952.3</v>
       </c>
     </row>
     <row r="4">
@@ -567,31 +567,31 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>132540</v>
+        <v>132938</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7503</v>
+        <v>32283</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>125037</v>
+        <v>100655</v>
       </c>
     </row>
     <row r="5">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>45218</v>
+        <v>55576</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34348</v>
+        <v>44706</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>54481</v>
+        <v>84241</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42091</v>
+        <v>71851</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>79436</v>
+        <v>104336</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>64876</v>
+        <v>89776</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>9960</v>
+        <v>21938</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -839,11 +839,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>184.0%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-8364</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="11">
@@ -861,19 +861,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>31700</v>
+        <v>43280</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -881,11 +881,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9253.299999999999</v>
+        <v>20833.3</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>79560</v>
+        <v>89520</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>79560</v>
+        <v>89520</v>
       </c>
     </row>
     <row r="13">
@@ -1029,19 +1029,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>37790</v>
+        <v>52730</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>37790</v>
+        <v>52730</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>214396</v>
+        <v>219376</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>169636</v>
+        <v>174616</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>172862</v>
+        <v>189082</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>162919</v>
+        <v>179139</v>
       </c>
     </row>
     <row r="18">
@@ -1155,31 +1155,31 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>147174</v>
+        <v>168714</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>29780</v>
+        <v>36380</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>117394</v>
+        <v>132334</v>
       </c>
     </row>
     <row r="19">
@@ -1197,19 +1197,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>62036</v>
+        <v>67016</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>43256</v>
+        <v>48236</v>
       </c>
     </row>
     <row r="20">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>144420</v>
+        <v>164340</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>135813.33</v>
+        <v>155733.33</v>
       </c>
     </row>
     <row r="21">
@@ -1323,31 +1323,31 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>87436</v>
+        <v>112216</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33629</v>
+        <v>35309</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>53807</v>
+        <v>76907</v>
       </c>
     </row>
     <row r="23">
@@ -1465,15 +1465,15 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>40280</v>
+        <v>46880</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>157816</v>
+        <v>151216</v>
       </c>
     </row>
     <row r="26">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>77220</v>
+        <v>79020</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>54220</v>
+        <v>56020</v>
       </c>
     </row>
     <row r="30">
@@ -1701,19 +1701,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>82778</v>
+        <v>92778</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>61478</v>
+        <v>71478</v>
       </c>
     </row>
     <row r="32">
@@ -1869,19 +1869,19 @@
         <v>102098</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1889,11 +1889,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>272.2%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-28300</v>
+        <v>-17902</v>
       </c>
     </row>
     <row r="36">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>165469</v>
+        <v>180449</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35561.7</v>
+        <v>40541.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>129907.3</v>
+        <v>139907.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>310168</v>
+        <v>366228</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -545,11 +545,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>281952.3</v>
+        <v>338012.3</v>
       </c>
     </row>
     <row r="4">
@@ -567,19 +567,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>132938</v>
+        <v>142898</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>100655</v>
+        <v>110615</v>
       </c>
     </row>
     <row r="5">
@@ -625,15 +625,15 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4681</v>
+        <v>9362</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17319</v>
+        <v>12638</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>55576</v>
+        <v>65536</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>44706</v>
+        <v>54666</v>
       </c>
     </row>
     <row r="7">
@@ -693,19 +693,19 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>84241</v>
+        <v>112521</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>71851</v>
+        <v>100131</v>
       </c>
     </row>
     <row r="8">
@@ -735,19 +735,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>104336</v>
+        <v>110596</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -755,11 +755,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>89776</v>
+        <v>96036</v>
       </c>
     </row>
     <row r="9">
@@ -777,19 +777,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>107556</v>
+        <v>112536</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -797,11 +797,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-19057.37</v>
+        <v>-14077.37</v>
       </c>
     </row>
     <row r="10">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18324</v>
+        <v>41824</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>190.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3614</v>
+        <v>-19886</v>
       </c>
     </row>
     <row r="11">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>89520</v>
+        <v>84540</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89520</v>
+        <v>84540</v>
       </c>
     </row>
     <row r="13">
@@ -987,19 +987,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>36878</v>
+        <v>41858</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>173.2%</t>
+          <t>152.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-26985</v>
+        <v>-22005</v>
       </c>
     </row>
     <row r="15">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>219376</v>
+        <v>224356</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>174616</v>
+        <v>179596</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>189082</v>
+        <v>200322</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>179139</v>
+        <v>190379</v>
       </c>
     </row>
     <row r="18">
@@ -1155,19 +1155,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>168714</v>
+        <v>183654</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1175,11 +1175,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>132334</v>
+        <v>147274</v>
       </c>
     </row>
     <row r="19">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>164340</v>
+        <v>174300</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>155733.33</v>
+        <v>165693.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,19 +1281,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>54000</v>
+        <v>58980</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>49020</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="22">
@@ -1323,19 +1323,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>112216</v>
+        <v>117196</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>76907</v>
+        <v>81887</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>141132</v>
+        <v>145592</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>121212</v>
+        <v>125672</v>
       </c>
     </row>
     <row r="24">
@@ -1423,15 +1423,15 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>26820</v>
+        <v>41640</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>69798</v>
+        <v>54978</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>198096</v>
+        <v>208096</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>154.1%</t>
+          <t>161.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>154.1%</t>
+          <t>161.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>151216</v>
+        <v>161216</v>
       </c>
     </row>
     <row r="26">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>104798</v>
+        <v>131618</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>98798</v>
+        <v>125618</v>
       </c>
     </row>
     <row r="31">
@@ -1785,19 +1785,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>116418</v>
+        <v>136218</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>116418</v>
+        <v>136218</v>
       </c>
     </row>
     <row r="34">
@@ -1869,19 +1869,19 @@
         <v>102098</v>
       </c>
       <c r="D35" t="n">
-        <v>10398</v>
+        <v>22398</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1889,11 +1889,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>272.2%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-17902</v>
+        <v>-5902</v>
       </c>
     </row>
     <row r="36">
@@ -2011,15 +2011,15 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1980</v>
+        <v>2160</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6300</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="39">
@@ -2037,19 +2037,19 @@
         <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>73840</v>
+        <v>93640</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2057,11 +2057,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>69780</v>
+        <v>89580</v>
       </c>
     </row>
     <row r="40">
@@ -2163,19 +2163,19 @@
         <v>400000</v>
       </c>
       <c r="D42" t="n">
-        <v>312150</v>
+        <v>434910</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>310170</v>
+        <v>432930</v>
       </c>
     </row>
     <row r="43">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -483,31 +483,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>180449</v>
+        <v>206285</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>40541.7</v>
+        <v>44691.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>139907.3</v>
+        <v>161593.3</v>
       </c>
     </row>
     <row r="3">
@@ -525,31 +525,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>366228</v>
+        <v>426386</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>140.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>140.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>28215.7</v>
+        <v>38158.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>338012.3</v>
+        <v>388227.3</v>
       </c>
     </row>
     <row r="4">
@@ -567,31 +567,31 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>142898</v>
+        <v>179258</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>32283</v>
+        <v>37263</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>110615</v>
+        <v>141995</v>
       </c>
     </row>
     <row r="5">
@@ -625,15 +625,15 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9362</v>
+        <v>22206</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>100.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12638</v>
+        <v>-206</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>65536</v>
+        <v>87496</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -671,11 +671,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>54666</v>
+        <v>76626</v>
       </c>
     </row>
     <row r="7">
@@ -693,31 +693,31 @@
         <v>242405</v>
       </c>
       <c r="D7" t="n">
-        <v>112521</v>
+        <v>178121</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12390</v>
+        <v>27210</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>100131</v>
+        <v>150911</v>
       </c>
     </row>
     <row r="8">
@@ -735,31 +735,31 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>110596</v>
+        <v>120556</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>14560</v>
+        <v>20370</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>96036</v>
+        <v>100186</v>
       </c>
     </row>
     <row r="9">
@@ -777,31 +777,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>112536</v>
+        <v>127874</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>126613.37</v>
+        <v>209343.37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>163.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-14077.37</v>
+        <v>-81469.37</v>
       </c>
     </row>
     <row r="10">
@@ -819,31 +819,31 @@
         <v>271440</v>
       </c>
       <c r="D10" t="n">
-        <v>21938</v>
+        <v>31838</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>41824</v>
+        <v>55539</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>190.6%</t>
+          <t>174.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-19886</v>
+        <v>-23701</v>
       </c>
     </row>
     <row r="11">
@@ -861,31 +861,31 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>43280</v>
+        <v>59500</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>22446.7</v>
+        <v>27426.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20833.3</v>
+        <v>32073.3</v>
       </c>
     </row>
     <row r="12">
@@ -903,19 +903,19 @@
         <v>239246</v>
       </c>
       <c r="D12" t="n">
-        <v>84540</v>
+        <v>119280</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>84540</v>
+        <v>119280</v>
       </c>
     </row>
     <row r="13">
@@ -1003,15 +1003,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>63863</v>
+        <v>67863</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>152.6%</t>
+          <t>162.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-22005</v>
+        <v>-26005</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>52730</v>
+        <v>87470</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>9980</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>52730</v>
+        <v>77490</v>
       </c>
     </row>
     <row r="16">
@@ -1071,19 +1071,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>224356</v>
+        <v>240916</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>179596</v>
+        <v>196156</v>
       </c>
     </row>
     <row r="17">
@@ -1113,19 +1113,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>200322</v>
+        <v>245122</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1133,11 +1133,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>190379</v>
+        <v>235179</v>
       </c>
     </row>
     <row r="18">
@@ -1155,31 +1155,31 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>183654</v>
+        <v>216434</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>36380</v>
+        <v>41360</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>147274</v>
+        <v>175074</v>
       </c>
     </row>
     <row r="19">
@@ -1197,27 +1197,27 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>67016</v>
+        <v>71996</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18780</v>
+        <v>23760</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1239,19 +1239,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>174300</v>
+        <v>184260</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>104.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>104.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>165693.33</v>
+        <v>175653.33</v>
       </c>
     </row>
     <row r="21">
@@ -1281,23 +1281,23 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>58980</v>
+        <v>65580</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4980</v>
+        <v>5480</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>54000</v>
+        <v>60100</v>
       </c>
     </row>
     <row r="22">
@@ -1323,31 +1323,31 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>117196</v>
+        <v>122176</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>35309</v>
+        <v>46949</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>81887</v>
+        <v>75227</v>
       </c>
     </row>
     <row r="23">
@@ -1365,19 +1365,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>145592</v>
+        <v>165392</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1385,11 +1385,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>125672</v>
+        <v>145472</v>
       </c>
     </row>
     <row r="24">
@@ -1407,31 +1407,31 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>96618</v>
+        <v>142218</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>41640</v>
+        <v>66440</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>54978</v>
+        <v>75778</v>
       </c>
     </row>
     <row r="25">
@@ -1449,19 +1449,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>208096</v>
+        <v>234916</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>161.9%</t>
+          <t>182.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>161.9%</t>
+          <t>182.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>161216</v>
+        <v>188036</v>
       </c>
     </row>
     <row r="26">
@@ -1507,15 +1507,15 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>102200</v>
+        <v>100200</v>
       </c>
     </row>
     <row r="27">
@@ -1549,15 +1549,15 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>34300</v>
+        <v>35980</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>112980</v>
+        <v>111300</v>
       </c>
     </row>
     <row r="28">
@@ -1575,19 +1575,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>129640</v>
+        <v>164440</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>161.1%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>161.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>107340</v>
+        <v>142140</v>
       </c>
     </row>
     <row r="29">
@@ -1617,19 +1617,19 @@
         <v>102098</v>
       </c>
       <c r="D29" t="n">
-        <v>79020</v>
+        <v>124440</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1637,11 +1637,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>56020</v>
+        <v>101440</v>
       </c>
     </row>
     <row r="30">
@@ -1659,19 +1659,19 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>131618</v>
+        <v>163418</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>125618</v>
+        <v>157418</v>
       </c>
     </row>
     <row r="31">
@@ -1743,19 +1743,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>133000</v>
+        <v>133500</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>130.3%</t>
+          <t>130.8%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>130.3%</t>
+          <t>130.8%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>133000</v>
+        <v>133500</v>
       </c>
     </row>
     <row r="33">
@@ -1785,31 +1785,31 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>136218</v>
+        <v>163038</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>159.7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>159.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>27800</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>136218</v>
+        <v>135238</v>
       </c>
     </row>
     <row r="34">
@@ -1953,31 +1953,31 @@
         <v>200000</v>
       </c>
       <c r="D37" t="n">
-        <v>58894</v>
+        <v>102694</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>31780</v>
+        <v>33460</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>27114</v>
+        <v>69234</v>
       </c>
     </row>
     <row r="38">
@@ -2121,31 +2121,31 @@
         <v>250000</v>
       </c>
       <c r="D41" t="n">
-        <v>36980</v>
+        <v>126380</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3960</v>
+        <v>4240</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>33020</v>
+        <v>122140</v>
       </c>
     </row>
     <row r="42">
@@ -2163,19 +2163,19 @@
         <v>400000</v>
       </c>
       <c r="D42" t="n">
-        <v>434910</v>
+        <v>436890</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>432930</v>
+        <v>434910</v>
       </c>
     </row>
     <row r="43">

--- a/导出_线上个人.xlsx
+++ b/导出_线上个人.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,43 +1941,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>102694</v>
+        <v>215700</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>33460</v>
+        <v>16400</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>69234</v>
+        <v>199300</v>
       </c>
     </row>
     <row r="38">
@@ -1988,38 +1988,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>魏恺志</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="D38" t="n">
-        <v>8280</v>
+        <v>102694</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2160</v>
+        <v>33460</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6120</v>
+        <v>69234</v>
       </c>
     </row>
     <row r="39">
@@ -2030,38 +2030,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>93640</v>
+        <v>8280</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4060</v>
+        <v>2160</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>89580</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="40">
@@ -2072,38 +2072,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>闫浩</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>93640</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>4060</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>89580</v>
       </c>
     </row>
     <row r="41">
@@ -2114,38 +2114,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>余文静</t>
+          <t>闫浩</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>126380</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4240</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>122140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2156,38 +2156,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="D42" t="n">
-        <v>436890</v>
+        <v>126380</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1980</v>
+        <v>4240</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>434910</v>
+        <v>122140</v>
       </c>
     </row>
     <row r="43">
@@ -2198,38 +2198,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="D43" t="n">
-        <v>57280</v>
+        <v>436890</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>57280</v>
+        <v>434910</v>
       </c>
     </row>
     <row r="44">
@@ -2240,37 +2240,79 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>吴云龙</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>57280</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>57280</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>龙刚</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C45" t="n">
         <v>100000</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D45" t="n">
         <v>2190</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H45" t="n">
         <v>2980</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>136.1%</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>-790</v>
       </c>
     </row>
